--- a/src/attributions/attributions_saliency_traj_400.xlsx
+++ b/src/attributions/attributions_saliency_traj_400.xlsx
@@ -1568,1709 +1568,1709 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.1621950417757034</v>
+        <v>7.69321050029248e-05</v>
       </c>
       <c r="B3" t="n">
-        <v>0.04166389256715775</v>
+        <v>1.300565418205224e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1772751957178116</v>
+        <v>3.869014108204283e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02574750781059265</v>
+        <v>2.942754326795693e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>0.241516649723053</v>
+        <v>1.75062486960087e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.197202205657959</v>
+        <v>1.205001717607956e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06607319414615631</v>
+        <v>4.486014404392336e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2008143812417984</v>
+        <v>6.221647709026001e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1977775692939758</v>
+        <v>8.154805982485414e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1280924379825592</v>
+        <v>7.965308759594336e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06901621073484421</v>
+        <v>7.016695235506631e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1025902554392815</v>
+        <v>2.872981713153422e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09019432961940765</v>
+        <v>2.614067852846347e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2445502132177353</v>
+        <v>6.938268052181229e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04884524643421173</v>
+        <v>3.37774486069975e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1496886909008026</v>
+        <v>4.799489943252411e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.07561760395765305</v>
+        <v>1.163006709248293e-05</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3588891923427582</v>
+        <v>2.835396117006894e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1124618723988533</v>
+        <v>4.077049197803717e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08954449743032455</v>
+        <v>2.199113851020229e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>0.137044757604599</v>
+        <v>8.01156693341909e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1622480154037476</v>
+        <v>3.957864919357235e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1050724163651466</v>
+        <v>2.28336261898221e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2191915512084961</v>
+        <v>1.190468628919916e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1356984972953796</v>
+        <v>1.955674179043854e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1327441185712814</v>
+        <v>1.475075714552077e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.07567925751209259</v>
+        <v>4.933976470056223e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.08592204749584198</v>
+        <v>9.578993740433361e-06</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2190979570150375</v>
+        <v>1.302366854361026e-07</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.01896525919437408</v>
+        <v>1.53781093104044e-06</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.07358782738447189</v>
+        <v>2.246888470835984e-05</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3444486558437347</v>
+        <v>1.303527642448898e-05</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.02029985375702381</v>
+        <v>4.015024751424789e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.04258966445922852</v>
+        <v>8.037852239795029e-06</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.03577024862170219</v>
+        <v>7.101992196112406e-06</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.3132336437702179</v>
+        <v>1.431111058991519e-06</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.09262128174304962</v>
+        <v>7.24573965271702e-06</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0221079345792532</v>
+        <v>9.189461707137525e-06</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1178517267107964</v>
+        <v>2.278088322782423e-05</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.2274772226810455</v>
+        <v>1.842049641709309e-05</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.07368168234825134</v>
+        <v>7.065947102091741e-06</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.08794412016868591</v>
+        <v>1.359354087071551e-07</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.01162524335086346</v>
+        <v>4.225719749229029e-06</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.0321451872587204</v>
+        <v>3.4815102480934e-06</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.1819995939731598</v>
+        <v>5.464462446980178e-06</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1866182833909988</v>
+        <v>2.637221768964082e-05</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.06450875848531723</v>
+        <v>1.843892096076161e-05</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.05312708765268326</v>
+        <v>1.134878402808681e-05</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1857650279998779</v>
+        <v>2.479579416103661e-05</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4476926326751709</v>
+        <v>4.476267349673435e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.02479011565446854</v>
+        <v>1.243101269210456e-05</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.06229893118143082</v>
+        <v>3.508415829855949e-06</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.06400616466999054</v>
+        <v>4.328972863731906e-06</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.04155842214822769</v>
+        <v>8.94939512363635e-06</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.2544042766094208</v>
+        <v>1.256288851436693e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0512479804456234</v>
+        <v>6.588148607988842e-06</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1540336757898331</v>
+        <v>1.800770405679941e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1223840415477753</v>
+        <v>1.60381259775022e-05</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.1198465973138809</v>
+        <v>1.63533022714546e-05</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1390191316604614</v>
+        <v>3.136509803880472e-06</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.04090685024857521</v>
+        <v>2.098459162880317e-06</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.2885784506797791</v>
+        <v>2.799941967168706e-08</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.2608537077903748</v>
+        <v>1.21830544230761e-05</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.1001094877719879</v>
+        <v>2.938819852715824e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.2443715929985046</v>
+        <v>6.646879228355829e-06</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.06050895527005196</v>
+        <v>4.696008545579389e-06</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.06400740891695023</v>
+        <v>7.181909040809842e-06</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.2027195692062378</v>
+        <v>9.225875601259759e-07</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.05162185430526733</v>
+        <v>5.167425115359947e-06</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1265050619840622</v>
+        <v>7.719924724369776e-06</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.01916422694921494</v>
+        <v>5.230379429121967e-06</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.05679979920387268</v>
+        <v>5.947675163042732e-06</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.1322775781154633</v>
+        <v>2.117953226843383e-05</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1164956241846085</v>
+        <v>2.564550186434644e-06</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.005949226208031178</v>
+        <v>2.494627369742375e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.1210862994194031</v>
+        <v>1.431593955203425e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.03211495280265808</v>
+        <v>1.314068776991917e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.1542532593011856</v>
+        <v>5.499994585989043e-06</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0173148587346077</v>
+        <v>8.303512004204094e-06</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.1921834200620651</v>
+        <v>1.019204501062632e-05</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.03080839850008488</v>
+        <v>1.072961458703503e-05</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.004612870514392853</v>
+        <v>1.725164111121558e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0181502103805542</v>
+        <v>2.991652536366018e-06</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.02083011344075203</v>
+        <v>6.44991223452962e-06</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.02274033427238464</v>
+        <v>9.210174539475702e-06</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.01297742873430252</v>
+        <v>6.451975423260592e-06</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.004817113280296326</v>
+        <v>5.468220933835255e-07</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.00764758512377739</v>
+        <v>2.896302703447873e-06</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.01401279866695404</v>
+        <v>1.222298578795744e-06</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.04872316867113113</v>
+        <v>9.782289680515532e-07</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.08825048804283142</v>
+        <v>3.653944986581337e-07</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.1085313782095909</v>
+        <v>1.172381689684698e-05</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.007407138124108315</v>
+        <v>1.555969538458157e-05</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.04886286333203316</v>
+        <v>1.391969726682873e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0370134525001049</v>
+        <v>1.450378476874903e-05</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.05143234133720398</v>
+        <v>1.862851240730379e-05</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.09917330741882324</v>
+        <v>4.304388767195633e-06</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.0441252775490284</v>
+        <v>4.050689312862232e-06</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.09737488627433777</v>
+        <v>7.464272584911669e-06</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.01505260914564133</v>
+        <v>1.507901288277935e-05</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.002421270590275526</v>
+        <v>5.598225016001379e-06</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.009123359806835651</v>
+        <v>1.11277304313262e-05</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.0711023285984993</v>
+        <v>8.884127055353019e-06</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.05240661650896072</v>
+        <v>1.573043050484557e-06</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.06112901121377945</v>
+        <v>2.090624093398219e-06</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.007698145695030689</v>
+        <v>2.999251137225656e-06</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.0213637463748455</v>
+        <v>1.614595589671808e-06</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.03481204435229301</v>
+        <v>8.169898251253471e-07</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1365949213504791</v>
+        <v>1.493539730290649e-05</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.2803511023521423</v>
+        <v>7.05310667399317e-05</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.1772286742925644</v>
+        <v>1.313276243308792e-05</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.1215249970555305</v>
+        <v>2.367164233874064e-05</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.3525061905384064</v>
+        <v>1.224510356223618e-06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.4354901909828186</v>
+        <v>3.909609949914739e-05</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.149657815694809</v>
+        <v>2.911847104769549e-06</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.1952707171440125</v>
+        <v>4.528732461039908e-06</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.215367466211319</v>
+        <v>1.349556623608805e-05</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.1874925196170807</v>
+        <v>1.009029801934958e-05</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.008741232566535473</v>
+        <v>8.461261131742503e-06</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.09481830894947052</v>
+        <v>1.7462387404521e-05</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.1580361574888229</v>
+        <v>1.13567821244942e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.3017203509807587</v>
+        <v>2.326554931642022e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.1556994915008545</v>
+        <v>6.433779617509572e-06</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.04974084720015526</v>
+        <v>1.17362924356712e-06</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.1734941601753235</v>
+        <v>1.157789120043162e-05</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.04609900712966919</v>
+        <v>6.676700650132261e-07</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.03851468861103058</v>
+        <v>8.824790711514652e-06</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.1334708034992218</v>
+        <v>4.999796146876179e-06</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.008272846229374409</v>
+        <v>4.052800431963988e-05</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.08457650989294052</v>
+        <v>3.535139740051818e-06</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.1652645170688629</v>
+        <v>2.461075746396091e-05</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.1095158383250237</v>
+        <v>9.154109648079611e-06</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.006454616785049438</v>
+        <v>6.626645699725486e-06</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.04781641811132431</v>
+        <v>1.552948742755689e-05</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.09095840156078339</v>
+        <v>1.201669692818541e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.04514618963003159</v>
+        <v>2.056025186902843e-05</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.02094353549182415</v>
+        <v>5.904219506192021e-06</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.006883539725095034</v>
+        <v>7.230953542602947e-07</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.04233530163764954</v>
+        <v>9.210038115270436e-06</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.06072130799293518</v>
+        <v>4.749515028379392e-06</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.1499884128570557</v>
+        <v>2.176608859372209e-06</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.005605081561952829</v>
+        <v>3.833839400613215e-06</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.04865280166268349</v>
+        <v>3.130498953396454e-07</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.0201406367123127</v>
+        <v>3.550476549207815e-06</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.128239780664444</v>
+        <v>1.51977919813362e-05</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.02165564708411694</v>
+        <v>9.679485629021656e-06</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.01331535167992115</v>
+        <v>2.269792730658082e-06</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.1192729920148849</v>
+        <v>8.957245881902054e-06</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.05651343241333961</v>
+        <v>1.793747969713877e-06</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.01032571773976088</v>
+        <v>2.259036773466505e-05</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.009365000762045383</v>
+        <v>8.290576261060778e-06</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.07948385924100876</v>
+        <v>4.807901405001758e-06</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.006589069962501526</v>
+        <v>1.530597000964917e-05</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.03025342524051666</v>
+        <v>1.54201734403614e-05</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.01189611479640007</v>
+        <v>1.126419647334842e-05</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.0006994376890361309</v>
+        <v>1.072406394087011e-05</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.07865618169307709</v>
+        <v>8.262953997473232e-06</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.05758543685078621</v>
+        <v>1.827303549362114e-06</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.03615984693169594</v>
+        <v>8.105379492917564e-06</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.0111315893009305</v>
+        <v>4.727933628601022e-06</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.005207177251577377</v>
+        <v>1.312407675868599e-07</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.05997680872678757</v>
+        <v>9.348673302156385e-07</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.03517725318670273</v>
+        <v>3.390143319847994e-05</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.1262361407279968</v>
+        <v>1.277260525966994e-05</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.03613594546914101</v>
+        <v>8.880541827238631e-06</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.06895468384027481</v>
+        <v>1.910800392579404e-06</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.07508771121501923</v>
+        <v>2.153839773200161e-07</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.09093862771987915</v>
+        <v>2.17129218071932e-05</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.01874150335788727</v>
+        <v>5.668006906489609e-06</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.1763552725315094</v>
+        <v>4.885096586804138e-06</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.0329538956284523</v>
+        <v>1.086499196389923e-06</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.06236175820231438</v>
+        <v>5.752177003159886e-06</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.06390546262264252</v>
+        <v>3.044485083592008e-06</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.09277743101119995</v>
+        <v>3.7660043744836e-05</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.053377915173769</v>
+        <v>5.265868821879849e-05</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.05921027436852455</v>
+        <v>2.420808596070856e-05</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.1300751268863678</v>
+        <v>1.819485305531998e-06</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.03700249269604683</v>
+        <v>1.2985932698939e-05</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.1137573048472404</v>
+        <v>7.280209501914214e-06</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.02252696827054024</v>
+        <v>1.382033246954961e-06</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.04559604451060295</v>
+        <v>2.940689591923729e-05</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.009626844897866249</v>
+        <v>4.310614258429268e-06</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.09387635439634323</v>
+        <v>3.411619218240958e-06</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.01462337747216225</v>
+        <v>2.42684873228427e-05</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.06456682085990906</v>
+        <v>3.097806256846525e-05</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.04870862513780594</v>
+        <v>1.09103257273091e-06</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.07147630304098129</v>
+        <v>1.198315385408932e-05</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.05921363830566406</v>
+        <v>1.354763662675396e-05</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.0293465368449688</v>
+        <v>8.643602996016853e-06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.003572234651073813</v>
+        <v>3.362196366651915e-05</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01736037060618401</v>
+        <v>0.001136099454015493</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007075238390825689</v>
+        <v>0.0001552150934003294</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008104057051241398</v>
+        <v>0.0009553147247061133</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001111818244680762</v>
+        <v>0.0001251767098437995</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004792677238583565</v>
+        <v>0.0002129704662365839</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003722902620211244</v>
+        <v>0.0003198805788997561</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0001727138296701014</v>
+        <v>0.000275085651082918</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001189781469292939</v>
+        <v>2.340342325624079e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004458880051970482</v>
+        <v>3.871694570989348e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01060701068490744</v>
+        <v>0.001175177283585072</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00149741827044636</v>
+        <v>0.0002661972539499402</v>
       </c>
       <c r="M4" t="n">
-        <v>0.006833284627646208</v>
+        <v>0.001293141860514879</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003950921818614006</v>
+        <v>0.0002987530606333166</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006875353865325451</v>
+        <v>0.0001218234974658117</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0007141479873098433</v>
+        <v>0.0003844574093818665</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002029065042734146</v>
+        <v>2.405908890068531e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001401029876433313</v>
+        <v>1.529189466964453e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>2.322545333299786e-05</v>
+        <v>5.740842607337981e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001563115627504885</v>
+        <v>5.703222996089607e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0001127341893152334</v>
+        <v>6.924312765477225e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00234695803374052</v>
+        <v>2.591912561911158e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001176090794615448</v>
+        <v>0.0001121300592785701</v>
       </c>
       <c r="X4" t="n">
-        <v>0.00113271118607372</v>
+        <v>0.0001279682182939723</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.002281093271449208</v>
+        <v>8.5596097051166e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0009506892529316247</v>
+        <v>0.0001515324402134866</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001338356523774564</v>
+        <v>0.0002581339504104108</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007957924390211701</v>
+        <v>5.869567030458711e-05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.002581616397947073</v>
+        <v>3.944009222323075e-06</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0005828625289723277</v>
+        <v>5.737440005759709e-05</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.000851096585392952</v>
+        <v>0.0002529795747250319</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.00155360100325197</v>
+        <v>0.000132053013658151</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.00086937565356493</v>
+        <v>0.0001671241625444964</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.685918636620045e-05</v>
+        <v>0.0001493391609983519</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001056204666383564</v>
+        <v>2.412573303445242e-05</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.001081553171388805</v>
+        <v>4.053273005411029e-05</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.001329843420535326</v>
+        <v>7.370589446509257e-05</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001554840477183461</v>
+        <v>0.0002785216202028096</v>
       </c>
       <c r="AM4" t="n">
-        <v>8.282873022835702e-05</v>
+        <v>0.000118369804113172</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0006016973638907075</v>
+        <v>0.0001806535583455116</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.0008178106509149075</v>
+        <v>0.0001341357128694654</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.002377439988777041</v>
+        <v>0.0002052744384855032</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0002301600179634988</v>
+        <v>7.948726124595851e-05</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.001002882490865886</v>
+        <v>0.0001249433553311974</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001021085772663355</v>
+        <v>1.962013993761502e-05</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.0003005536855198443</v>
+        <v>8.491384505759925e-06</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.01263829786330462</v>
+        <v>0.000624367967247963</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0009713449398986995</v>
+        <v>1.164597779279575e-05</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.003086738288402557</v>
+        <v>0.0004641260311473161</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.002680213423445821</v>
+        <v>0.0006579720648005605</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.0008024749695323408</v>
+        <v>0.0001020088820951059</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.00159469258505851</v>
+        <v>1.388216332998127e-06</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.001219559460878372</v>
+        <v>8.567584154661745e-05</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.001858482253737748</v>
+        <v>3.996341547463089e-05</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.001798610202968121</v>
+        <v>6.346285954350606e-05</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.002735120942816138</v>
+        <v>6.436781404772773e-06</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.002392948139458895</v>
+        <v>0.0002206501376349479</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.592622958123684e-05</v>
+        <v>3.773976641241461e-05</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.003920956049114466</v>
+        <v>0.0001833263959269971</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.003766872920095921</v>
+        <v>0.0001449886767659336</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001170886680483818</v>
+        <v>6.187515100464225e-05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001778694218955934</v>
+        <v>0.0003210259892512113</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.762499545700848e-06</v>
+        <v>7.710439240327105e-05</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.001219439902342856</v>
+        <v>5.051770131103694e-06</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.001691277720965445</v>
+        <v>0.0001151226460933685</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0004477601614780724</v>
+        <v>3.089435631409287e-05</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.00200155726633966</v>
+        <v>6.571930862264708e-05</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0014241001335904</v>
+        <v>0.0001055830070981756</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.001048860256560147</v>
+        <v>9.814609802560881e-05</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.000463497155578807</v>
+        <v>2.575524194980972e-05</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0003463695466052741</v>
+        <v>6.304057023953646e-05</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.000941409554798156</v>
+        <v>5.346730176825076e-05</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0004128675791434944</v>
+        <v>4.708165943156928e-05</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.005963305477052927</v>
+        <v>0.0003590890555642545</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0002319259947398677</v>
+        <v>8.456120121991262e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.001274128211662173</v>
+        <v>0.0002815255720634013</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0008992821094579995</v>
+        <v>0.0001260045246453956</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.003672189544886351</v>
+        <v>0.0001801147445803508</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.0003915723937097937</v>
+        <v>0.0001835944567574188</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001031232648529112</v>
+        <v>2.466527621436398e-05</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.001507960492745042</v>
+        <v>0.0001645915035624057</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.001158629776909947</v>
+        <v>5.332210275810212e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.002840152941644192</v>
+        <v>0.0003573490539565682</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0009627472027204931</v>
+        <v>6.701484380755574e-05</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0007579732919111848</v>
+        <v>0.0002984939492307603</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0008981171995401382</v>
+        <v>1.214866369991796e-05</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001253352966159582</v>
+        <v>9.706855053082108e-06</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0004986185231246054</v>
+        <v>3.529959030856844e-06</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0002503466093912721</v>
+        <v>2.081343518511858e-05</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.0006418257253244519</v>
+        <v>3.60657722922042e-05</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.000749296392314136</v>
+        <v>9.431235957890749e-05</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0007934977766126394</v>
+        <v>0.0002267109521199018</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.001496606855653226</v>
+        <v>0.0003326871665194631</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.002242479706183076</v>
+        <v>0.0004202452255412936</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.00192416156642139</v>
+        <v>0.0001417784515069798</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.002303340239450336</v>
+        <v>0.0001603536802576855</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.001169180381111801</v>
+        <v>0.0001101069210562855</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.002795734442770481</v>
+        <v>0.0001760667364578694</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0002610581577755511</v>
+        <v>9.343543206341565e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0009152380516752601</v>
+        <v>6.792737985961139e-05</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.002118065720424056</v>
+        <v>0.0003715933416970074</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.0009684470715001225</v>
+        <v>7.090602593962103e-05</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.001716495491564274</v>
+        <v>0.0003189912240486592</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0006913709221407771</v>
+        <v>6.701589154545218e-05</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.001557646552100778</v>
+        <v>1.832862835726701e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0004674787633121014</v>
+        <v>1.283941855945159e-05</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.0002259471511933953</v>
+        <v>5.541471182368696e-06</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0005060856929048896</v>
+        <v>7.644086872460321e-05</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0008537675603292882</v>
+        <v>0.0001918961352203041</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.002114941831678152</v>
+        <v>0.0001050556966220029</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0008356929174624383</v>
+        <v>4.118328070035204e-05</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.005734729114919901</v>
+        <v>0.0002466245787218213</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0007412733975797892</v>
+        <v>0.0001824110222514719</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0008845830452628434</v>
+        <v>0.0003148422401864082</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0009256663615815341</v>
+        <v>9.572062117513269e-05</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.002132208552211523</v>
+        <v>0.0002826955169439316</v>
       </c>
       <c r="DM4" t="n">
-        <v>8.735476876609027e-05</v>
+        <v>9.564131323713809e-05</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.002100558253005147</v>
+        <v>1.980026536330115e-05</v>
       </c>
       <c r="DO4" t="n">
-        <v>8.909092139219865e-05</v>
+        <v>0.0001728591305436566</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.001309834886342287</v>
+        <v>6.80212615407072e-05</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0001581347896717489</v>
+        <v>0.000215093488804996</v>
       </c>
       <c r="DR4" t="n">
-        <v>3.568938700482249e-05</v>
+        <v>0.0001365797797916457</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.002927093068137765</v>
+        <v>7.944779645185918e-05</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0001918605994433165</v>
+        <v>0.0002451674954500049</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.0001191769551951438</v>
+        <v>7.507282862206921e-05</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.001318423892371356</v>
+        <v>0.0003429324424359947</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.001364183379337192</v>
+        <v>2.02220726350788e-05</v>
       </c>
       <c r="DX4" t="n">
-        <v>6.496581772807986e-05</v>
+        <v>9.856973338173702e-05</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.003153061727061868</v>
+        <v>4.757806163979694e-05</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.000778087938670069</v>
+        <v>0.0002058583195321262</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.002328017260879278</v>
+        <v>5.027482620789669e-05</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0004783762851729989</v>
+        <v>0.0002724509395193309</v>
       </c>
       <c r="EC4" t="n">
-        <v>9.153564315056428e-05</v>
+        <v>5.936357047175989e-05</v>
       </c>
       <c r="ED4" t="n">
-        <v>4.876360617345199e-05</v>
+        <v>0.0004861738416366279</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0003175627207383513</v>
+        <v>0.0002912562631536275</v>
       </c>
       <c r="EF4" t="n">
-        <v>5.118001718074083e-05</v>
+        <v>0.0001420319022145122</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001736726961098611</v>
+        <v>0.0002138113777618855</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0004843703645747155</v>
+        <v>7.957559137139469e-05</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.0004934007301926613</v>
+        <v>0.0002929330221377313</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0003073464904446155</v>
+        <v>0.0001075475593097508</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.00110023224260658</v>
+        <v>3.278395161032677e-05</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0007799080922268331</v>
+        <v>5.492967829923145e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0006377972313202918</v>
+        <v>1.435070316802012e-06</v>
       </c>
       <c r="EN4" t="n">
-        <v>7.138070941437036e-05</v>
+        <v>4.031524440506473e-05</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.001092988299205899</v>
+        <v>4.581221219268627e-05</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.002495845779776573</v>
+        <v>0.0003556189476512372</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.000679287186358124</v>
+        <v>1.155531936092302e-05</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.001950673293322325</v>
+        <v>4.618744424078614e-05</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.002152883913367987</v>
+        <v>0.0001111382589442655</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.005339976865798235</v>
+        <v>5.619862713501789e-05</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.0002915791119448841</v>
+        <v>0.0001233365182997659</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.00143450521863997</v>
+        <v>4.02863443014212e-05</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0004649438778869808</v>
+        <v>0.0002195600536651909</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0008784859674051404</v>
+        <v>3.725157148437575e-05</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.002476747613400221</v>
+        <v>0.00036970543442294</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.0002410043380223215</v>
+        <v>5.316640817909501e-05</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.001216395176015794</v>
+        <v>0.0003346012672409415</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.0006277484353631735</v>
+        <v>3.386435128049925e-05</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.001692235702648759</v>
+        <v>3.743938577827066e-05</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.0005905822617933154</v>
+        <v>2.610572482808493e-05</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.0001255128590855747</v>
+        <v>4.782275937031955e-05</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.0006963195046409965</v>
+        <v>7.839780300855637e-05</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.0007073722663335502</v>
+        <v>1.343080657534301e-05</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.001277662813663483</v>
+        <v>0.0001295523252338171</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.0004326797206886113</v>
+        <v>0.0001044850650941953</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.001788910711184144</v>
+        <v>0.0001154670608229935</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0003628848062362522</v>
+        <v>6.744293204974383e-05</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0005013243644498289</v>
+        <v>0.0001807070657378063</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.0006568895769305527</v>
+        <v>5.837804565089755e-05</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0005765114910900593</v>
+        <v>0.0002349545829929411</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.001413187594152987</v>
+        <v>7.114977779565379e-05</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.0005204136250540614</v>
+        <v>0.0001101495145121589</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.002284504938870668</v>
+        <v>0.0001919596834341064</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.0003541677433531731</v>
+        <v>8.282950147986412e-08</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.002732086926698685</v>
+        <v>0.0003479774459265172</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.004459661431610584</v>
+        <v>9.558551391819492e-05</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0009535577264614403</v>
+        <v>0.0002318242040928453</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.0001629658654564992</v>
+        <v>2.141429467883427e-05</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0009739403612911701</v>
+        <v>5.579640128416941e-05</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.000723009929060936</v>
+        <v>0.0003551569534465671</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.001463423715904355</v>
+        <v>2.929385664174333e-05</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.001520468504168093</v>
+        <v>0.000164240540470928</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.001301752985455096</v>
+        <v>1.348963269265369e-05</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.0007170616881921887</v>
+        <v>0.0003215205215383321</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.002226592972874641</v>
+        <v>0.0002961035061161965</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.001486727502197027</v>
+        <v>7.578417717013508e-05</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.00311807612888515</v>
+        <v>0.0003539921599440277</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.0005813090829178691</v>
+        <v>2.854048943845555e-05</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0008882541442289948</v>
+        <v>5.046844671596773e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.706500552245416e-05</v>
+        <v>0.001525543862953782</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0003432284574955702</v>
+        <v>0.003484549000859261</v>
       </c>
       <c r="C5" t="n">
-        <v>4.561223249766044e-05</v>
+        <v>0.0006168839172460139</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000133984416606836</v>
+        <v>4.709040877060033e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001957709901034832</v>
+        <v>0.000660828547552228</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001832998386817053</v>
+        <v>0.004392480943351984</v>
       </c>
       <c r="G5" t="n">
-        <v>1.75109671545215e-05</v>
+        <v>0.0008021365501917899</v>
       </c>
       <c r="H5" t="n">
-        <v>7.197977538453415e-05</v>
+        <v>0.00117594888433814</v>
       </c>
       <c r="I5" t="n">
-        <v>2.343643427593634e-05</v>
+        <v>0.000970709603279829</v>
       </c>
       <c r="J5" t="n">
-        <v>1.399024768033996e-06</v>
+        <v>0.00128849851898849</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0003216319892089814</v>
+        <v>0.004476563073694706</v>
       </c>
       <c r="L5" t="n">
-        <v>5.190800584387034e-05</v>
+        <v>0.0008730487897992134</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001556168572278693</v>
+        <v>0.0006197375478222966</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00023328946554102</v>
+        <v>0.0009509458905085921</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002335358440177515</v>
+        <v>0.004343046806752682</v>
       </c>
       <c r="P5" t="n">
-        <v>7.065316458465531e-05</v>
+        <v>5.978273838991299e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.450626511243172e-05</v>
+        <v>0.0001422874047420919</v>
       </c>
       <c r="R5" t="n">
-        <v>5.107394463266246e-05</v>
+        <v>0.001641123439185321</v>
       </c>
       <c r="S5" t="n">
-        <v>2.756879257503897e-05</v>
+        <v>0.0001303582102991641</v>
       </c>
       <c r="T5" t="n">
-        <v>7.938736962387338e-05</v>
+        <v>0.0006090992828831077</v>
       </c>
       <c r="U5" t="n">
-        <v>2.213684820162598e-05</v>
+        <v>0.0005988584598526359</v>
       </c>
       <c r="V5" t="n">
-        <v>8.781606993579771e-06</v>
+        <v>0.001419487874954939</v>
       </c>
       <c r="W5" t="n">
-        <v>1.856785456766374e-05</v>
+        <v>0.0006694441544823349</v>
       </c>
       <c r="X5" t="n">
-        <v>7.204127905424684e-05</v>
+        <v>0.0002956710231956095</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.884625453385524e-05</v>
+        <v>0.000269107345957309</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.272633527260041e-06</v>
+        <v>0.0005204832996241748</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.173910277429968e-05</v>
+        <v>6.798518734285608e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.062067819177173e-05</v>
+        <v>0.0002099455014104024</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.9486210627947e-05</v>
+        <v>0.0006242748349905014</v>
       </c>
       <c r="AD5" t="n">
-        <v>9.257015335606411e-05</v>
+        <v>0.0004007891984656453</v>
       </c>
       <c r="AE5" t="n">
-        <v>6.965068314457312e-05</v>
+        <v>0.001718825078569353</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.803393575362861e-05</v>
+        <v>0.001324651995673776</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.633582698763348e-05</v>
+        <v>0.0006517448928207159</v>
       </c>
       <c r="AH5" t="n">
-        <v>5.947839235886931e-05</v>
+        <v>0.0002845482667908072</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.930619302787818e-08</v>
+        <v>0.002250931924208999</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4.585223359754309e-05</v>
+        <v>0.0002821309317369014</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.687577605480328e-05</v>
+        <v>0.0002438495575916022</v>
       </c>
       <c r="AL5" t="n">
-        <v>7.748797361273319e-05</v>
+        <v>0.0008720760815776885</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.597869049874134e-05</v>
+        <v>0.0008301333291456103</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.038774593733251e-06</v>
+        <v>0.001055435393936932</v>
       </c>
       <c r="AO5" t="n">
-        <v>2.488880818418693e-05</v>
+        <v>0.0004124612314626575</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.832982110907324e-05</v>
+        <v>0.0006623779190704226</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.006404181680409e-05</v>
+        <v>0.0003086441429331899</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.576783107448136e-06</v>
+        <v>0.001178088481537998</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.699716100731166e-06</v>
+        <v>0.0006714273476973176</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.706962474505417e-05</v>
+        <v>0.0008353302255272865</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0002390483132330701</v>
+        <v>0.003853824688121676</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.264109869225649e-05</v>
+        <v>0.0009362123673781753</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.869091258617118e-05</v>
+        <v>0.00033616425935179</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.177178430429194e-05</v>
+        <v>0.0007781673339195549</v>
       </c>
       <c r="AY5" t="n">
-        <v>6.565111834788695e-05</v>
+        <v>0.002569508273154497</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.471915159840137e-05</v>
+        <v>0.000382192141842097</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.638113412307575e-05</v>
+        <v>9.403820877196267e-05</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.909121005563065e-05</v>
+        <v>0.0004834829596802592</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.258482163597364e-05</v>
+        <v>8.375797915505245e-05</v>
       </c>
       <c r="BD5" t="n">
-        <v>9.247093112207949e-05</v>
+        <v>0.0004189154133200645</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.990355228073895e-05</v>
+        <v>0.0004670324851758778</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.190139614162035e-05</v>
+        <v>0.0002226796350441873</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0002173642860725522</v>
+        <v>0.0004118649812880903</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0001178908642032184</v>
+        <v>0.000906018540263176</v>
       </c>
       <c r="BI5" t="n">
-        <v>5.899788084207103e-05</v>
+        <v>0.0002029417228186503</v>
       </c>
       <c r="BJ5" t="n">
-        <v>2.147508348571137e-05</v>
+        <v>0.0005249378737062216</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.202620064257644e-05</v>
+        <v>0.00062881427584216</v>
       </c>
       <c r="BL5" t="n">
-        <v>5.606190825346857e-05</v>
+        <v>0.0001428371469955891</v>
       </c>
       <c r="BM5" t="n">
-        <v>3.263908183726016e-06</v>
+        <v>0.0008824568940326571</v>
       </c>
       <c r="BN5" t="n">
-        <v>3.684354669530876e-05</v>
+        <v>5.594168760580942e-05</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.403307578584645e-05</v>
+        <v>7.314635149668902e-05</v>
       </c>
       <c r="BP5" t="n">
-        <v>1.335791057499591e-05</v>
+        <v>0.0007269084453582764</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2.159636642318219e-05</v>
+        <v>0.0009986772201955318</v>
       </c>
       <c r="BR5" t="n">
-        <v>4.159581294516101e-05</v>
+        <v>0.001681323512457311</v>
       </c>
       <c r="BS5" t="n">
-        <v>6.658838628936792e-06</v>
+        <v>0.000140770454891026</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.521816198481247e-06</v>
+        <v>0.00120471406262368</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.408553311601281e-05</v>
+        <v>7.769439253024757e-05</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.0001353780680801719</v>
+        <v>0.002639492275193334</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.594777444959618e-05</v>
+        <v>0.0004959077923558652</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.717197978403419e-05</v>
+        <v>0.001268759486265481</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.155393854598515e-06</v>
+        <v>4.344465560279787e-05</v>
       </c>
       <c r="BZ5" t="n">
-        <v>5.362335650715977e-05</v>
+        <v>0.001558713964186609</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.258752596797422e-05</v>
+        <v>0.0005323621444404125</v>
       </c>
       <c r="CB5" t="n">
-        <v>9.424020390724763e-06</v>
+        <v>0.0003171713906340301</v>
       </c>
       <c r="CC5" t="n">
-        <v>6.605914677493274e-06</v>
+        <v>0.0004640277475118637</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.315395588288084e-06</v>
+        <v>0.0005759524065069854</v>
       </c>
       <c r="CE5" t="n">
-        <v>6.219077476998791e-05</v>
+        <v>0.001090727979317307</v>
       </c>
       <c r="CF5" t="n">
-        <v>5.330443855200429e-07</v>
+        <v>8.46414768602699e-05</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.840822162397671e-05</v>
+        <v>0.0006973290001042187</v>
       </c>
       <c r="CH5" t="n">
-        <v>3.29699287249241e-06</v>
+        <v>0.0005574660026468337</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.494331602065358e-05</v>
+        <v>0.001102351350709796</v>
       </c>
       <c r="CJ5" t="n">
-        <v>4.2956460674759e-05</v>
+        <v>0.0005026686703786254</v>
       </c>
       <c r="CK5" t="n">
-        <v>9.292289178119972e-07</v>
+        <v>0.0004002420173492283</v>
       </c>
       <c r="CL5" t="n">
-        <v>6.572909114765935e-06</v>
+        <v>0.0002242171758553013</v>
       </c>
       <c r="CM5" t="n">
-        <v>4.011416967841797e-05</v>
+        <v>5.844107363373041e-05</v>
       </c>
       <c r="CN5" t="n">
-        <v>5.211916868574917e-05</v>
+        <v>0.001671201782301068</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.279752996197203e-05</v>
+        <v>0.0006137437885627151</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.472180429118453e-05</v>
+        <v>0.0001414656871929765</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.432701148791239e-05</v>
+        <v>4.108261782675982e-05</v>
       </c>
       <c r="CR5" t="n">
-        <v>2.424849117232952e-05</v>
+        <v>0.0003845139290206134</v>
       </c>
       <c r="CS5" t="n">
-        <v>8.734571019886062e-05</v>
+        <v>0.0009694742038846016</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0001378260785713792</v>
+        <v>2.774111635517329e-05</v>
       </c>
       <c r="CU5" t="n">
-        <v>2.993319139932282e-05</v>
+        <v>9.346359729534015e-05</v>
       </c>
       <c r="CV5" t="n">
-        <v>6.194067282194737e-06</v>
+        <v>0.0003414915408939123</v>
       </c>
       <c r="CW5" t="n">
-        <v>4.511744919000193e-05</v>
+        <v>0.0009650233550928533</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.411939592799172e-05</v>
+        <v>3.509964153636247e-05</v>
       </c>
       <c r="CY5" t="n">
-        <v>3.221221413696185e-05</v>
+        <v>0.0006152401911094785</v>
       </c>
       <c r="CZ5" t="n">
-        <v>5.58147621632088e-06</v>
+        <v>0.0004420736513566226</v>
       </c>
       <c r="DA5" t="n">
-        <v>3.313197521492839e-05</v>
+        <v>0.001084447139874101</v>
       </c>
       <c r="DB5" t="n">
-        <v>2.744969970081002e-05</v>
+        <v>0.0002331063587917015</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.913820935646072e-07</v>
+        <v>0.0004429442342370749</v>
       </c>
       <c r="DD5" t="n">
-        <v>9.25015592656564e-06</v>
+        <v>0.0002057248202618212</v>
       </c>
       <c r="DE5" t="n">
-        <v>5.375503678806126e-05</v>
+        <v>0.0001593983615748584</v>
       </c>
       <c r="DF5" t="n">
-        <v>8.096924284473062e-05</v>
+        <v>0.0009735007770359516</v>
       </c>
       <c r="DG5" t="n">
-        <v>7.348539656959474e-05</v>
+        <v>0.0003558224998414516</v>
       </c>
       <c r="DH5" t="n">
-        <v>3.352252315380611e-05</v>
+        <v>0.0006530927494168282</v>
       </c>
       <c r="DI5" t="n">
-        <v>1.467483252781676e-05</v>
+        <v>0.0008127037435770035</v>
       </c>
       <c r="DJ5" t="n">
-        <v>7.100480434019119e-05</v>
+        <v>0.0009967799996957183</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.815734039060771e-05</v>
+        <v>2.461537951603532e-05</v>
       </c>
       <c r="DL5" t="n">
-        <v>1.431881264579715e-05</v>
+        <v>0.0009613496367819607</v>
       </c>
       <c r="DM5" t="n">
-        <v>1.878946568467654e-05</v>
+        <v>0.000585350499022752</v>
       </c>
       <c r="DN5" t="n">
-        <v>2.288915993631235e-06</v>
+        <v>0.0002487259334884584</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.044884215341881e-05</v>
+        <v>0.0006400785641744733</v>
       </c>
       <c r="DP5" t="n">
-        <v>1.18041089081089e-06</v>
+        <v>0.0003987201489508152</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0001066417462425306</v>
+        <v>0.001002333825454116</v>
       </c>
       <c r="DR5" t="n">
-        <v>3.24863322020974e-05</v>
+        <v>0.0001842974597821012</v>
       </c>
       <c r="DS5" t="n">
-        <v>5.802635132567957e-05</v>
+        <v>0.0007692488725297153</v>
       </c>
       <c r="DT5" t="n">
-        <v>1.943720781127922e-05</v>
+        <v>4.160602838965133e-05</v>
       </c>
       <c r="DU5" t="n">
-        <v>2.84051875496516e-05</v>
+        <v>0.0003482319007162005</v>
       </c>
       <c r="DV5" t="n">
-        <v>9.250372386304662e-06</v>
+        <v>0.0003306132857687771</v>
       </c>
       <c r="DW5" t="n">
-        <v>2.138306081178598e-05</v>
+        <v>0.0005350325955078006</v>
       </c>
       <c r="DX5" t="n">
-        <v>1.795658863557037e-05</v>
+        <v>0.0002175591216655448</v>
       </c>
       <c r="DY5" t="n">
-        <v>1.286680981138488e-05</v>
+        <v>0.0004326634807512164</v>
       </c>
       <c r="DZ5" t="n">
-        <v>7.530091534135863e-05</v>
+        <v>0.0003395665844436735</v>
       </c>
       <c r="EA5" t="n">
-        <v>2.394142939010635e-05</v>
+        <v>0.0004704327438957989</v>
       </c>
       <c r="EB5" t="n">
-        <v>4.789149170392193e-05</v>
+        <v>0.00142030802089721</v>
       </c>
       <c r="EC5" t="n">
-        <v>5.24910501553677e-05</v>
+        <v>0.0002683393540792167</v>
       </c>
       <c r="ED5" t="n">
-        <v>8.412323222728446e-05</v>
+        <v>0.0004875180311501026</v>
       </c>
       <c r="EE5" t="n">
-        <v>2.258243330288678e-05</v>
+        <v>0.001064212410710752</v>
       </c>
       <c r="EF5" t="n">
-        <v>2.029091774602421e-05</v>
+        <v>0.0005655887071043253</v>
       </c>
       <c r="EG5" t="n">
-        <v>4.692400398198515e-05</v>
+        <v>5.329958366928622e-05</v>
       </c>
       <c r="EH5" t="n">
-        <v>8.994668860395905e-06</v>
+        <v>0.0004401872574817389</v>
       </c>
       <c r="EI5" t="n">
-        <v>4.290928336558864e-05</v>
+        <v>0.0007381820469163358</v>
       </c>
       <c r="EJ5" t="n">
-        <v>1.463573426008224e-06</v>
+        <v>0.0008599098073318601</v>
       </c>
       <c r="EK5" t="n">
-        <v>1.739530489430763e-05</v>
+        <v>0.0003438791027292609</v>
       </c>
       <c r="EL5" t="n">
-        <v>6.520202441606671e-05</v>
+        <v>4.4693959353026e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>8.294307917822152e-06</v>
+        <v>9.240785584552214e-05</v>
       </c>
       <c r="EN5" t="n">
-        <v>4.652127245208248e-06</v>
+        <v>0.000296265963697806</v>
       </c>
       <c r="EO5" t="n">
-        <v>1.251799403689802e-06</v>
+        <v>0.0003826715110335499</v>
       </c>
       <c r="EP5" t="n">
-        <v>6.205291811056668e-06</v>
+        <v>0.0004797271976713091</v>
       </c>
       <c r="EQ5" t="n">
-        <v>4.630917828762904e-05</v>
+        <v>7.846807420719415e-05</v>
       </c>
       <c r="ER5" t="n">
-        <v>3.075563290622085e-05</v>
+        <v>0.0008497514063492417</v>
       </c>
       <c r="ES5" t="n">
-        <v>5.21784349984955e-05</v>
+        <v>0.00125952553935349</v>
       </c>
       <c r="ET5" t="n">
-        <v>8.498816168867052e-05</v>
+        <v>0.000803048606030643</v>
       </c>
       <c r="EU5" t="n">
-        <v>5.29840326635167e-06</v>
+        <v>0.0003260411613155156</v>
       </c>
       <c r="EV5" t="n">
-        <v>1.309210165345576e-05</v>
+        <v>0.0003323161799926311</v>
       </c>
       <c r="EW5" t="n">
-        <v>2.531288009777199e-05</v>
+        <v>0.000358554330887273</v>
       </c>
       <c r="EX5" t="n">
-        <v>9.130380931310356e-07</v>
+        <v>0.0005049243336543441</v>
       </c>
       <c r="EY5" t="n">
-        <v>4.929015631205402e-05</v>
+        <v>0.001257783500477672</v>
       </c>
       <c r="EZ5" t="n">
-        <v>3.08856988340267e-06</v>
+        <v>9.254534234059975e-06</v>
       </c>
       <c r="FA5" t="n">
-        <v>2.904889515775722e-05</v>
+        <v>0.0005480408435687423</v>
       </c>
       <c r="FB5" t="n">
-        <v>3.738860641533392e-06</v>
+        <v>0.0006911532254889607</v>
       </c>
       <c r="FC5" t="n">
-        <v>3.615526657085866e-05</v>
+        <v>0.0009399383561685681</v>
       </c>
       <c r="FD5" t="n">
-        <v>3.209498390788212e-05</v>
+        <v>0.0004212876374367625</v>
       </c>
       <c r="FE5" t="n">
-        <v>9.735340427141637e-06</v>
+        <v>0.0003668915596790612</v>
       </c>
       <c r="FF5" t="n">
-        <v>9.064486221177503e-06</v>
+        <v>0.0001512541202828288</v>
       </c>
       <c r="FG5" t="n">
-        <v>1.097136828320799e-05</v>
+        <v>7.140776870073751e-05</v>
       </c>
       <c r="FH5" t="n">
-        <v>2.306083661096636e-05</v>
+        <v>0.001241408404894173</v>
       </c>
       <c r="FI5" t="n">
-        <v>2.317416874575429e-05</v>
+        <v>0.0006720602978020906</v>
       </c>
       <c r="FJ5" t="n">
-        <v>9.624363156035542e-05</v>
+        <v>0.0004901114734821022</v>
       </c>
       <c r="FK5" t="n">
-        <v>5.780263745691627e-05</v>
+        <v>0.0003276171919424087</v>
       </c>
       <c r="FL5" t="n">
-        <v>3.4653305192478e-05</v>
+        <v>0.001328086829744279</v>
       </c>
       <c r="FM5" t="n">
-        <v>4.274810271454044e-05</v>
+        <v>0.0007020135526545346</v>
       </c>
       <c r="FN5" t="n">
-        <v>6.734589987900108e-05</v>
+        <v>0.001534337527118623</v>
       </c>
       <c r="FO5" t="n">
-        <v>3.383863077033311e-05</v>
+        <v>0.0007394831045530736</v>
       </c>
       <c r="FP5" t="n">
-        <v>3.053232285310514e-05</v>
+        <v>0.0002750723797362298</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0001024771190714091</v>
+        <v>0.0009768855525180697</v>
       </c>
       <c r="FR5" t="n">
-        <v>3.288967855041847e-05</v>
+        <v>0.001526778563857079</v>
       </c>
       <c r="FS5" t="n">
-        <v>9.982154733734205e-05</v>
+        <v>0.0006154729635454714</v>
       </c>
       <c r="FT5" t="n">
-        <v>3.922309042536654e-05</v>
+        <v>0.0002799358044285327</v>
       </c>
       <c r="FU5" t="n">
-        <v>5.286862869979814e-05</v>
+        <v>0.0004048645205330104</v>
       </c>
       <c r="FV5" t="n">
-        <v>6.38155615888536e-05</v>
+        <v>5.083449650555849e-05</v>
       </c>
       <c r="FW5" t="n">
-        <v>1.344194242847152e-05</v>
+        <v>0.001151181990280747</v>
       </c>
       <c r="FX5" t="n">
-        <v>4.630328839994036e-05</v>
+        <v>0.001167519483715296</v>
       </c>
       <c r="FY5" t="n">
-        <v>1.856440576375462e-05</v>
+        <v>0.0006646178662776947</v>
       </c>
       <c r="FZ5" t="n">
-        <v>4.018461550003849e-05</v>
+        <v>0.0002169874933315441</v>
       </c>
       <c r="GA5" t="n">
-        <v>9.619265620131046e-05</v>
+        <v>0.000521306530572474</v>
       </c>
       <c r="GB5" t="n">
-        <v>6.81825986248441e-06</v>
+        <v>0.0007438805187121034</v>
       </c>
       <c r="GC5" t="n">
-        <v>1.1318227279844e-06</v>
+        <v>0.001573181012645364</v>
       </c>
       <c r="GD5" t="n">
-        <v>2.488189238647465e-05</v>
+        <v>0.001194405136629939</v>
       </c>
       <c r="GE5" t="n">
-        <v>1.3119621144142e-05</v>
+        <v>6.441189907491207e-05</v>
       </c>
       <c r="GF5" t="n">
-        <v>4.587228977470659e-05</v>
+        <v>0.0002359320933464915</v>
       </c>
       <c r="GG5" t="n">
-        <v>1.467104812036268e-05</v>
+        <v>0.0009114081040024757</v>
       </c>
     </row>
     <row r="6">
@@ -3844,571 +3844,571 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.4802160859107971</v>
+        <v>0.0003096509317401797</v>
       </c>
       <c r="B7" t="n">
-        <v>2.49001932144165</v>
+        <v>0.002863860223442316</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2041821330785751</v>
+        <v>0.0002779419301077724</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8774770498275757</v>
+        <v>0.002777805319055915</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2370086014270782</v>
+        <v>0.0004131427558604628</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6000593304634094</v>
+        <v>0.0007840385660529137</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0609402135014534</v>
+        <v>0.00127787166275084</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1365048736333847</v>
+        <v>0.001168572111055255</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04584205150604248</v>
+        <v>4.564518894767389e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.677767276763916</v>
+        <v>0.0004039236227981746</v>
       </c>
       <c r="K7" t="n">
-        <v>1.626793742179871</v>
+        <v>0.002889700932428241</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04501878097653389</v>
+        <v>0.0007478822371922433</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8595240712165833</v>
+        <v>0.003962695598602295</v>
       </c>
       <c r="N7" t="n">
-        <v>0.453196108341217</v>
+        <v>0.0008632451645098627</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9144638776779175</v>
+        <v>0.0005070048500783741</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1053339168429375</v>
+        <v>0.00163761293515563</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1354575753211975</v>
+        <v>0.000133165274746716</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1456799656152725</v>
+        <v>2.570124343037605e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04903936386108398</v>
+        <v>6.035465776221827e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2624314427375793</v>
+        <v>5.988939665257931e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1321608275175095</v>
+        <v>0.0002165880287066102</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3316835761070251</v>
+        <v>6.759892130503431e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1898823976516724</v>
+        <v>0.0004343242908362299</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1697462946176529</v>
+        <v>0.0006138292956165969</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2604742646217346</v>
+        <v>0.000210548285394907</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2186012864112854</v>
+        <v>0.000645758060272783</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2489670515060425</v>
+        <v>0.0007330334046855569</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.06365740299224854</v>
+        <v>0.0003374018997419626</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3874821364879608</v>
+        <v>0.0001587421866133809</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.03079741448163986</v>
+        <v>0.0003343564749229699</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1040319055318832</v>
+        <v>0.0001952602033270523</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.09495142102241516</v>
+        <v>0.0002019607927650213</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.02455220371484756</v>
+        <v>0.0007353612454608083</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.08567257225513458</v>
+        <v>0.000151199143147096</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.01015725452452898</v>
+        <v>0.0002579044667072594</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1203829795122147</v>
+        <v>0.0002129483327735215</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.2896366119384766</v>
+        <v>0.0001236720709130168</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.2706880271434784</v>
+        <v>0.0007284802850335836</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.04789427295327187</v>
+        <v>0.000484829768538475</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.1698967069387436</v>
+        <v>0.0006575342267751694</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.1325138211250305</v>
+        <v>0.0001465919194743037</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.2710584700107574</v>
+        <v>0.0006970755057409406</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.03898655250668526</v>
+        <v>0.0004307343042455614</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.03621012344956398</v>
+        <v>0.0001022612195811234</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.1522056311368942</v>
+        <v>2.448297891533002e-05</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.04337400570511818</v>
+        <v>6.193178705871105e-05</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.715846419334412</v>
+        <v>0.001566874678246677</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.01901964470744133</v>
+        <v>1.990876626223326e-06</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.1546428799629211</v>
+        <v>0.001735628815367818</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.2550527453422546</v>
+        <v>0.002328117843717337</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.03394831717014313</v>
+        <v>0.0004904413945041597</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.029703538864851</v>
+        <v>0.0001508597633801401</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.1471692025661469</v>
+        <v>0.0001665457966737449</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.307311624288559</v>
+        <v>0.0003150630509480834</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.1694959104061127</v>
+        <v>0.0002917692181654274</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.4068968594074249</v>
+        <v>0.0001313946122536436</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.3655027747154236</v>
+        <v>0.0004207747697364539</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.03094595670700073</v>
+        <v>0.0005069971666671336</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.6570713520050049</v>
+        <v>0.0008528504986315966</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.3353335857391357</v>
+        <v>0.0003313591587357223</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.1588214337825775</v>
+        <v>0.0003589965053834021</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.257306694984436</v>
+        <v>0.001060228911228478</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.02382323518395424</v>
+        <v>0.0004510839353315532</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.262386828660965</v>
+        <v>7.128642755560577e-05</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.2394250631332397</v>
+        <v>2.719486656133085e-05</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.09699710458517075</v>
+        <v>0.0001312071981374174</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.3257164061069489</v>
+        <v>0.0004024498630315065</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1663362085819244</v>
+        <v>3.084398485952988e-05</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.1209889501333237</v>
+        <v>0.0001989604061236605</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.1051986292004585</v>
+        <v>5.328653787728399e-05</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.06810581684112549</v>
+        <v>0.000259474414633587</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.1568330079317093</v>
+        <v>1.719446299830452e-05</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.04404358938336372</v>
+        <v>0.0001637556706555188</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.8236935138702393</v>
+        <v>0.0008899050299078226</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.1330385655164719</v>
+        <v>0.000240163499256596</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.2030243128538132</v>
+        <v>0.00152892735786736</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.02566875144839287</v>
+        <v>0.0006656088517047465</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.3803755640983582</v>
+        <v>0.0006535748834721744</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.1244314312934875</v>
+        <v>0.0004253302176948637</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.01640796475112438</v>
+        <v>0.000188380159670487</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.2331307828426361</v>
+        <v>0.0004525165422819555</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.1548524349927902</v>
+        <v>0.0001034637680277228</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.4093523919582367</v>
+        <v>0.0009268775465898216</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.1753901392221451</v>
+        <v>0.0001763066393323243</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.03934106230735779</v>
+        <v>0.001097967266105115</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.1259098947048187</v>
+        <v>6.609088450204581e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.1715948730707169</v>
+        <v>4.462871947907843e-05</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.06818289309740067</v>
+        <v>0.0001087554264813662</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.02903700619935989</v>
+        <v>0.0001047887053573504</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.1170044615864754</v>
+        <v>0.0001041411596816033</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.2097551673650742</v>
+        <v>0.0001832224952522665</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.06953466683626175</v>
+        <v>0.0005651761312037706</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.2195318341255188</v>
+        <v>0.001038945512846112</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.4206073880195618</v>
+        <v>0.001737171784043312</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.2785008251667023</v>
+        <v>0.0003904562327079475</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.2223837077617645</v>
+        <v>0.0003714061167556792</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.1865136921405792</v>
+        <v>1.680011337157339e-05</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.1700621545314789</v>
+        <v>0.0005885126884095371</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.08325726538896561</v>
+        <v>0.0003375292290002108</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.1260732710361481</v>
+        <v>8.52836383273825e-05</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.3346347212791443</v>
+        <v>0.0009332388872280717</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.1620124727487564</v>
+        <v>0.0002273877908010036</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.1704171001911163</v>
+        <v>0.001189413946121931</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.1235872283577919</v>
+        <v>0.0001947146956808865</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.2044519931077957</v>
+        <v>5.148869240656495e-05</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.08733807504177094</v>
+        <v>0.0001964006514754146</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.06058556586503983</v>
+        <v>5.181767119211145e-05</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.07804366946220398</v>
+        <v>0.0002027166774496436</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.2471900135278702</v>
+        <v>0.0001780552411219105</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.09979133307933807</v>
+        <v>0.0007230191258713603</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.009102796204388142</v>
+        <v>0.0001828543463489041</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.3577910661697388</v>
+        <v>0.0008536558598279953</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.3212510049343109</v>
+        <v>0.0001094843028113246</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.04990703612565994</v>
+        <v>0.001256734365597367</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.1528406590223312</v>
+        <v>0.0002388881985098124</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.02859755232930183</v>
+        <v>0.001330836559645832</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.03253084048628807</v>
+        <v>0.0006365053122863173</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.2419404089450836</v>
+        <v>9.023866732604802e-05</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.07908870279788971</v>
+        <v>0.0004073710297234356</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.2111064791679382</v>
+        <v>0.0001879211777122691</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.01208179816603661</v>
+        <v>0.0003426411713007838</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.07094146311283112</v>
+        <v>0.0001014068111544475</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.345503181219101</v>
+        <v>0.0002527917386032641</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.02432676032185555</v>
+        <v>0.0005686671938747168</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.08338140696287155</v>
+        <v>0.0005407850258052349</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.1592918485403061</v>
+        <v>0.001430129865184426</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.1435035765171051</v>
+        <v>4.732774686999619e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.008455201052129269</v>
+        <v>2.37752974499017e-05</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.4712575972080231</v>
+        <v>0.0002574503014329821</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.1246892288327217</v>
+        <v>0.000576724938582629</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.3188559114933014</v>
+        <v>7.58827300160192e-05</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.09883897006511688</v>
+        <v>0.0008170410874299705</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0006418395787477493</v>
+        <v>7.735839608358219e-05</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.07097483426332474</v>
+        <v>0.001732158707454801</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.1392193734645844</v>
+        <v>0.001201743725687265</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.009510062634944916</v>
+        <v>0.0006207188707776368</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.217070147395134</v>
+        <v>0.0006877370760776103</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.005428875330835581</v>
+        <v>0.0003176903701387346</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.03386199101805687</v>
+        <v>0.001094963168725371</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.04117913544178009</v>
+        <v>7.370687671937048e-05</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.09487626701593399</v>
+        <v>4.171186446910724e-05</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.09908910095691681</v>
+        <v>1.25652804854326e-05</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.02990523539483547</v>
+        <v>8.892075129551813e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.03407151997089386</v>
+        <v>9.988060628529638e-05</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.147786021232605</v>
+        <v>0.0002973803784698248</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.3000756800174713</v>
+        <v>0.0009777380619198084</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.05948801711201668</v>
+        <v>2.019833482336253e-05</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.1956118196249008</v>
+        <v>0.0007325905608013272</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.2676735818386078</v>
+        <v>0.0005067970487289131</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.6099597215652466</v>
+        <v>0.0001812654954846948</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.1788685023784637</v>
+        <v>0.0004757299029733986</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.3583844900131226</v>
+        <v>0.0002889756578952074</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.06139926612377167</v>
+        <v>0.0008050082251429558</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.1072694286704063</v>
+        <v>8.252994302893057e-05</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.3396895229816437</v>
+        <v>0.000997163588181138</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.06514988839626312</v>
+        <v>0.0001540493976790458</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.09828847646713257</v>
+        <v>0.001298545743338764</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.1112685427069664</v>
+        <v>0.0001076507323887199</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.2077346742153168</v>
+        <v>9.412088547833264e-05</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.119819387793541</v>
+        <v>0.0002195671258959919</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.02817059680819511</v>
+        <v>0.0002019590174313635</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.1241941452026367</v>
+        <v>0.0002448809100314975</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.05495902523398399</v>
+        <v>7.474895392078906e-05</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.200295090675354</v>
+        <v>0.000490498379804194</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.150987297296524</v>
+        <v>0.0003808235924225301</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.2706958651542664</v>
+        <v>0.0006412281072698534</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.1180684491991997</v>
+        <v>0.000369716202840209</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.05103092640638351</v>
+        <v>0.0005209246301092207</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.00690172566100955</v>
+        <v>0.0003695410268846899</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.2440304756164551</v>
+        <v>0.000485996890347451</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.3156125247478485</v>
+        <v>0.0002366214466746897</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.1841456592082977</v>
+        <v>0.0006113209528848529</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.1128841713070869</v>
+        <v>0.001267916988581419</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.08837977796792984</v>
+        <v>0.0001831077679526061</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.1653503775596619</v>
+        <v>0.001260157907381654</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.6756802797317505</v>
+        <v>0.0006839758716523647</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.2185043841600418</v>
+        <v>0.0009635471506044269</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.1051516681909561</v>
+        <v>8.898091618902981e-05</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.07470905780792236</v>
+        <v>0.0006595776067115366</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.1291186362504959</v>
+        <v>0.001219887170009315</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.2837357521057129</v>
+        <v>0.0003407591721042991</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.1508272439241409</v>
+        <v>0.0001765024499036372</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.2155885994434357</v>
+        <v>0.0001678473490756005</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.07769900560379028</v>
+        <v>0.001124057220295072</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.2839240729808807</v>
+        <v>0.0007409560494124889</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.1241344958543777</v>
+        <v>0.0001886914542410523</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.6434189081192017</v>
+        <v>0.000838180654682219</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.06303861737251282</v>
+        <v>0.0002668548258952796</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.1353228837251663</v>
+        <v>0.0003000317956320941</v>
       </c>
     </row>
     <row r="8">
@@ -4982,1140 +4982,1140 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.002836563624441624</v>
+        <v>0.02468075975775719</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01166623644530773</v>
+        <v>0.1107316464185715</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001179021899588406</v>
+        <v>0.05889055505394936</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004676206968724728</v>
+        <v>0.008980337530374527</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004324353765696287</v>
+        <v>0.01582108996808529</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002969377441331744</v>
+        <v>0.06391601264476776</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0005139896529726684</v>
+        <v>0.02472920715808868</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001256581977941096</v>
+        <v>0.02579363621771336</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0003723552508745342</v>
+        <v>0.03151912614703178</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00247417064383626</v>
+        <v>0.0145526509732008</v>
       </c>
       <c r="K9" t="n">
-        <v>0.007702059112489223</v>
+        <v>0.1308333724737167</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009824172593653202</v>
+        <v>0.06095176935195923</v>
       </c>
       <c r="M9" t="n">
-        <v>0.006200568284839392</v>
+        <v>0.006367618683725595</v>
       </c>
       <c r="N9" t="n">
-        <v>0.005875391885638237</v>
+        <v>0.03245138004422188</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004520355258136988</v>
+        <v>0.03452269732952118</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001722950721159577</v>
+        <v>0.01539668813347816</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003245121799409389</v>
+        <v>0.02246429398655891</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0003492091782391071</v>
+        <v>0.04631910845637321</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0004305793845560402</v>
+        <v>0.009971832856535912</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002463819459080696</v>
+        <v>0.04570771008729935</v>
       </c>
       <c r="U9" t="n">
-        <v>0.000519320834428072</v>
+        <v>0.003582187928259373</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001306849997490644</v>
+        <v>0.001556456089019775</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0009431102080270648</v>
+        <v>0.00362053420394659</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001767270732671022</v>
+        <v>0.01093502342700958</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0006889778887853026</v>
+        <v>0.007955075241625309</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0002340914070373401</v>
+        <v>0.02024238929152489</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0004668720939662308</v>
+        <v>0.01261320244520903</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0006648986600339413</v>
+        <v>0.0004380263853818178</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.00243614986538887</v>
+        <v>0.001535385847091675</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.001353767118416727</v>
+        <v>0.006781380623579025</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.003301134100183845</v>
+        <v>0.01566881500184536</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.001194564858451486</v>
+        <v>0.03698381036520004</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0004458551993593574</v>
+        <v>0.01758346892893314</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001554133137688041</v>
+        <v>0.008209066465497017</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0001262672885786742</v>
+        <v>0.05122504010796547</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.00119121209718287</v>
+        <v>0.0004080613143742085</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.001639081165194511</v>
+        <v>0.01617026701569557</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001980365719646215</v>
+        <v>0.03912731632590294</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.000201922346604988</v>
+        <v>0.009053990244865417</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0003455829573795199</v>
+        <v>0.01264787372201681</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0006823252770118415</v>
+        <v>0.03584825247526169</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0009516722057014704</v>
+        <v>0.01166635937988758</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0006017584819346666</v>
+        <v>0.006191875785589218</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.000354883522959426</v>
+        <v>0.04256564751267433</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0009661646327003837</v>
+        <v>0.004057040438055992</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.001897850073873997</v>
+        <v>0.0243252944201231</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.009991532191634178</v>
+        <v>0.1408443003892899</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0004711774236056954</v>
+        <v>0.02147174067795277</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0005568896303884685</v>
+        <v>0.01657095924019814</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001386599848046899</v>
+        <v>0.01628592051565647</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.00139738735742867</v>
+        <v>0.03926151245832443</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0006340764230117202</v>
+        <v>0.01460085157305002</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0006481839809566736</v>
+        <v>0.03205205500125885</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.0005549244815483689</v>
+        <v>0.01412245444953442</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001037685899063945</v>
+        <v>0.02505930699408054</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001827092375606298</v>
+        <v>0.04241951555013657</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.001577268820255995</v>
+        <v>0.01375257782638073</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0005180567968636751</v>
+        <v>0.009060671553015709</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.004775119479745626</v>
+        <v>0.06563548743724823</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.001870519598014653</v>
+        <v>0.02224135026335716</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0003705284034367651</v>
+        <v>0.01017486397176981</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.002951355185359716</v>
+        <v>0.01454550493508577</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0005961360293440521</v>
+        <v>0.01397014688700438</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0008423217805102468</v>
+        <v>0.0002775995526462793</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.001931849867105484</v>
+        <v>0.001282364595681429</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0003409285563975573</v>
+        <v>0.02880405262112617</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.002877010963857174</v>
+        <v>0.01105548534542322</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.003443550784140825</v>
+        <v>0.0294685885310173</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0002534691011533141</v>
+        <v>0.02919023297727108</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.00122041767463088</v>
+        <v>0.009583139792084694</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0006171851418912411</v>
+        <v>0.009774122387170792</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.875810918747447e-05</v>
+        <v>0.01168422680348158</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0008231072570197284</v>
+        <v>0.03020288236439228</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.003865264356136322</v>
+        <v>0.1405902504920959</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0007533651078119874</v>
+        <v>0.01425379235297441</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0007232988718897104</v>
+        <v>0.002495496533811092</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0004300018772482872</v>
+        <v>0.03046657331287861</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.002104033250361681</v>
+        <v>0.01012227311730385</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0006962536135688424</v>
+        <v>0.01366449985653162</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.00106892257463187</v>
+        <v>3.840320277959108e-05</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0002814191102515906</v>
+        <v>0.005139641463756561</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0003539711469784379</v>
+        <v>0.01758958771824837</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.002522308612242341</v>
+        <v>0.0326199047267437</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0005322507931850851</v>
+        <v>0.0107263270765543</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.001402822439558804</v>
+        <v>0.009240356273949146</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.000114421512989793</v>
+        <v>0.00452029425650835</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0006202594377100468</v>
+        <v>0.01302183605730534</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0006070273229852319</v>
+        <v>0.001037907088175416</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.0001537789794383571</v>
+        <v>0.006790828891098499</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0002228752564406022</v>
+        <v>0.002965447492897511</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.002457454800605774</v>
+        <v>0.01493863202631474</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.001865508500486612</v>
+        <v>0.05845498666167259</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.001471159979701042</v>
+        <v>0.03754445910453796</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.001452766009606421</v>
+        <v>0.02098601870238781</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.002487466670572758</v>
+        <v>0.02002285979688168</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.00138855492696166</v>
+        <v>0.05441693961620331</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0002779362839646637</v>
+        <v>0.001607509329915047</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.000783502880949527</v>
+        <v>0.0136055126786232</v>
       </c>
       <c r="CU9" t="n">
-        <v>5.522037099581212e-05</v>
+        <v>0.01629097573459148</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0002803399693220854</v>
+        <v>0.007334097288548946</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.001871843356639147</v>
+        <v>0.02926688268780708</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0005049720639362931</v>
+        <v>0.01292655616998672</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.00192898279055953</v>
+        <v>0.0104422690346837</v>
       </c>
       <c r="CZ9" t="n">
-        <v>3.219558129785582e-05</v>
+        <v>0.007108249235898256</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0007285359897650778</v>
+        <v>0.01368078403174877</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0007611667970195413</v>
+        <v>0.004957341589033604</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0002965840685646981</v>
+        <v>0.007753771729767323</v>
       </c>
       <c r="DD9" t="n">
-        <v>8.675781282363459e-05</v>
+        <v>0.002330799121409655</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.00134501582942903</v>
+        <v>0.01680076122283936</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.003978358116000891</v>
+        <v>0.06637593358755112</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0008182985475286841</v>
+        <v>0.02212353423237801</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.001440500607714057</v>
+        <v>0.02673247270286083</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.003705029608681798</v>
+        <v>0.04639380797743797</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0006295006023719907</v>
+        <v>0.07500565052032471</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.003585879458114505</v>
+        <v>0.01548746041953564</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0001273346424568444</v>
+        <v>0.0323687270283699</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.001856522168964148</v>
+        <v>0.02766235172748566</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.002006146125495434</v>
+        <v>0.003503862768411636</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.001811694819480181</v>
+        <v>0.02297097444534302</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0009511411772109568</v>
+        <v>0.02511887811124325</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.002025438705459237</v>
+        <v>0.0005761617794632912</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0009276551427319646</v>
+        <v>0.006868313997983932</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0009189049014821649</v>
+        <v>0.008763432502746582</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0008741703350096941</v>
+        <v>0.0007871524430811405</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0004265800816938281</v>
+        <v>0.0220468994230032</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0006537680164910853</v>
+        <v>0.006888133008033037</v>
       </c>
       <c r="DW9" t="n">
-        <v>1.481952494941652e-05</v>
+        <v>0.006624054163694382</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0006000204593874514</v>
+        <v>0.01248675398528576</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.00170551217161119</v>
+        <v>0.004541950300335884</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.001000450109131634</v>
+        <v>0.006971575319766998</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.00235291849821806</v>
+        <v>0.02563984505832195</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0003673462197184563</v>
+        <v>0.02151950635015965</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0004113535978831351</v>
+        <v>0.0005004031118005514</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.001136698178015649</v>
+        <v>0.01259511522948742</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0003713367623277009</v>
+        <v>0.04700975492596626</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.001192477997392416</v>
+        <v>0.02590544894337654</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0001287346676690504</v>
+        <v>0.0169440396130085</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0001565686688991264</v>
+        <v>0.001580140553414822</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.001543986960314214</v>
+        <v>0.01837899535894394</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0001441522181266919</v>
+        <v>0.0006991230184212327</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0002509309852030128</v>
+        <v>0.002886627335101366</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0009095645509660244</v>
+        <v>0.004696958232671022</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0004225574666634202</v>
+        <v>0.005139223765581846</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0001538264623377472</v>
+        <v>0.003134499303996563</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.001717125764116645</v>
+        <v>0.001782942563295364</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.000964172650128603</v>
+        <v>0.01856441795825958</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0001018250841298141</v>
+        <v>0.001063082367181778</v>
       </c>
       <c r="ER9" t="n">
-        <v>2.730474807322025e-05</v>
+        <v>0.02643395774066448</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0008954108343459666</v>
+        <v>0.06014023348689079</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.001554521499201655</v>
+        <v>0.04321951046586037</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0006066568312235177</v>
+        <v>0.02150997519493103</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.001535080373287201</v>
+        <v>0.006787413265556097</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0003736407670658082</v>
+        <v>0.0105341924354434</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0003043069154955447</v>
+        <v>0.01467994786798954</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.001721976092085242</v>
+        <v>0.03726848959922791</v>
       </c>
       <c r="EZ9" t="n">
-        <v>2.14525807678001e-05</v>
+        <v>0.0111994007602334</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.001286853337660432</v>
+        <v>0.008991979993879795</v>
       </c>
       <c r="FB9" t="n">
-        <v>7.02486140653491e-05</v>
+        <v>0.001610759296454489</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0009553692070767283</v>
+        <v>0.01262732781469822</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0006228725542314351</v>
+        <v>0.001239702804014087</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.0001590316096553579</v>
+        <v>0.002485339995473623</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0003410219214856625</v>
+        <v>0.0065759033896029</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.001688379794359207</v>
+        <v>0.003593491390347481</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.001684660324826837</v>
+        <v>0.03856877982616425</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0008277299930341542</v>
+        <v>0.01772655360400677</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0001661157875787467</v>
+        <v>0.0267652440816164</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0001230844500241801</v>
+        <v>0.02551108971238136</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0007716475520282984</v>
+        <v>0.04004715383052826</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0005203110631555319</v>
+        <v>0.009619076736271381</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.0002673252311069518</v>
+        <v>0.04198563098907471</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0008174936519935727</v>
+        <v>0.02783580124378204</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.00203169253654778</v>
+        <v>0.03422819823026657</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.001666554948315024</v>
+        <v>0.005500562489032745</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.001909710234031081</v>
+        <v>0.00456897122785449</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0005951063940301538</v>
+        <v>0.02483298256993294</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.005558078177273273</v>
+        <v>0.05165354907512665</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.001319271279498935</v>
+        <v>0.01597071997821331</v>
       </c>
       <c r="FV9" t="n">
-        <v>4.612095654010773e-05</v>
+        <v>0.006399399600923061</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.0009074081899598241</v>
+        <v>0.04451560601592064</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0002446793369017541</v>
+        <v>0.01135632768273354</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0003716041392181069</v>
+        <v>0.04630633816123009</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.002867121947929263</v>
+        <v>0.03429232910275459</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.000230906589422375</v>
+        <v>0.01797830127179623</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.002874873112887144</v>
+        <v>0.01969915069639683</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0002643723855726421</v>
+        <v>0.01662810519337654</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.001119378954172134</v>
+        <v>0.01021077577024698</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.001480467733927071</v>
+        <v>0.005879078060388565</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.002402463695034385</v>
+        <v>0.02289709635078907</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.000198008943698369</v>
+        <v>0.01916665770113468</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.001203933730721474</v>
+        <v>0.001181916799396276</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02158538810908794</v>
+        <v>0.006023535504937172</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001491353963501751</v>
+        <v>0.0009844782762229443</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01190851908177137</v>
+        <v>0.005092707928270102</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00299820932559669</v>
+        <v>0.0007180522079579532</v>
       </c>
       <c r="F10" t="n">
-        <v>0.003437810111790895</v>
+        <v>0.004211180843412876</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001387781812809408</v>
+        <v>0.002491543767973781</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00183605367783457</v>
+        <v>0.002785948570817709</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001597379916347563</v>
+        <v>0.0004296798724681139</v>
       </c>
       <c r="J10" t="n">
-        <v>0.002544156275689602</v>
+        <v>0.001101527945138514</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01460734102874994</v>
+        <v>0.005914868786931038</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001068781013600528</v>
+        <v>0.002249319106340408</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0122043788433075</v>
+        <v>0.00710219144821167</v>
       </c>
       <c r="N10" t="n">
-        <v>0.006779931951314211</v>
+        <v>0.00198262301273644</v>
       </c>
       <c r="O10" t="n">
-        <v>0.005791525822132826</v>
+        <v>0.003997587598860264</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001223827362991869</v>
+        <v>0.003009399864822626</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001680506276898086</v>
+        <v>0.0009090054081752896</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0006056884303689003</v>
+        <v>0.0007193057099357247</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0009515444980934262</v>
+        <v>0.0005682734190486372</v>
       </c>
       <c r="T10" t="n">
-        <v>0.003366418648511171</v>
+        <v>4.333425749791786e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0008720289333723485</v>
+        <v>0.0003691263846121728</v>
       </c>
       <c r="V10" t="n">
-        <v>0.002368927001953125</v>
+        <v>5.339249401004054e-05</v>
       </c>
       <c r="W10" t="n">
-        <v>0.00102769723162055</v>
+        <v>0.0008507390157319605</v>
       </c>
       <c r="X10" t="n">
-        <v>0.002385926432907581</v>
+        <v>0.001886000041849911</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.002124604769051075</v>
+        <v>0.0003937194123864174</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0009652136359363794</v>
+        <v>0.001340010552667081</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0004549319564830512</v>
+        <v>0.0009862363804131746</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.002307864837348461</v>
+        <v>0.00117306096944958</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.002928878413513303</v>
+        <v>0.0008509311592206359</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0004031474236398935</v>
+        <v>0.001142960391007364</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0004517258494161069</v>
+        <v>0.0001146895810961723</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.001179007929749787</v>
+        <v>0.0004018518375232816</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0005805589607916772</v>
+        <v>0.002765509532764554</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0004692382644861937</v>
+        <v>3.796187229454517e-06</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0002300175547134131</v>
+        <v>0.001476732781156898</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0008629861404187977</v>
+        <v>0.000720364332664758</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.001297313952818513</v>
+        <v>0.0006336398073472083</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.001955267274752259</v>
+        <v>0.001905137207359076</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0006379747064784169</v>
+        <v>0.001415191916748881</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.001025735517032444</v>
+        <v>0.001218531164340675</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.002356555080041289</v>
+        <v>0.0004118072683922946</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.002572578610852361</v>
+        <v>0.001390467397868633</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.001002719858661294</v>
+        <v>0.0009520435705780983</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.001676749438047409</v>
+        <v>0.0002808230638038367</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0007263645529747009</v>
+        <v>0.0003361717099323869</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.002260633511468768</v>
+        <v>0.0004364387132227421</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.01733279414474964</v>
+        <v>0.003457037499174476</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0005113115767017007</v>
+        <v>0.001161961350589991</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.002092249225825071</v>
+        <v>0.002952789422124624</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.00294788065366447</v>
+        <v>0.004689864348620176</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.002191234845668077</v>
+        <v>0.003144836518913507</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0005931745981797576</v>
+        <v>3.763141285162419e-05</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0001246874453499913</v>
+        <v>5.148031050339341e-05</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.000398474105168134</v>
+        <v>0.0006975100841373205</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0003704882110469043</v>
+        <v>0.0009021657751873136</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.00395138980820775</v>
+        <v>5.286437226459384e-05</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.003671363228932023</v>
+        <v>0.001096403924748302</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.001805730047635734</v>
+        <v>0.0009444624884054065</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.005426593124866486</v>
+        <v>0.002185790799558163</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.004694314673542976</v>
+        <v>0.0005103960284031928</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.002561167115345597</v>
+        <v>0.0007647803286090493</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.001363773015327752</v>
+        <v>0.001731919590383768</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0002761509967967868</v>
+        <v>0.0008807852864265442</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.004033531062304974</v>
+        <v>0.0004476260801311582</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.004811964463442564</v>
+        <v>0.0001328090293100104</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.001704986090771854</v>
+        <v>7.065244972181972e-06</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0004665589367505163</v>
+        <v>0.0009839617414399981</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.004034982994198799</v>
+        <v>0.000106349543784745</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.001952280756086111</v>
+        <v>6.035611659171991e-05</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0001698031555861235</v>
+        <v>0.0002174557303078473</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0008299612672999501</v>
+        <v>0.0007740670116618276</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.001269449596293271</v>
+        <v>0.0003155859012622386</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.002139580436050892</v>
+        <v>3.148951509501785e-05</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.008504386991262436</v>
+        <v>0.002375015756115317</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.001036231638863683</v>
+        <v>0.0008296284358948469</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.001600797520950437</v>
+        <v>0.003142681438475847</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0009291812893934548</v>
+        <v>0.001017829170450568</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.005238592159003019</v>
+        <v>0.002232445869594812</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0004800666938535869</v>
+        <v>0.0005169302457943559</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.00115744152572006</v>
+        <v>0.0004102546081412584</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0007475708844140172</v>
+        <v>0.0008750705164857209</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.001478233840316534</v>
+        <v>1.434288424206898e-05</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.00349888694472611</v>
+        <v>0.00200285273604095</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0009175974410027266</v>
+        <v>0.0001479637430747971</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.001140986918471754</v>
+        <v>0.002051484771072865</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0007111365557648242</v>
+        <v>7.062440272420645e-05</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.001178708742372692</v>
+        <v>0.0007475942838937044</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0008256225846707821</v>
+        <v>0.000246551469899714</v>
       </c>
       <c r="CK10" t="n">
-        <v>8.798454655334353e-05</v>
+        <v>0.0003781963023357093</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.000370174995623529</v>
+        <v>4.228961915941909e-05</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.003130749333649874</v>
+        <v>0.0006478590657934546</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.003052118234336376</v>
+        <v>0.001014902023598552</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.001148933661170304</v>
+        <v>0.002634458243846893</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.004966748412698507</v>
+        <v>0.003042162396013737</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.003592128865420818</v>
+        <v>0.0001494050375185907</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.002879376988857985</v>
+        <v>0.0005908060702495277</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.001588659011758864</v>
+        <v>0.0002465046127326787</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.004405460320413113</v>
+        <v>0.0008878792868927121</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0002687226806301624</v>
+        <v>0.0003892386448569596</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.001355756423436105</v>
+        <v>4.000202170573175e-05</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.002672743052244186</v>
+        <v>0.00191366660874337</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.001233238261193037</v>
+        <v>0.0004372622643131763</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.002058858284726739</v>
+        <v>0.00222398666664958</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0005824408144690096</v>
+        <v>0.0004077405901625752</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.001169164548628032</v>
+        <v>0.0008491293410770595</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0006928436923772097</v>
+        <v>0.0003846338950097561</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0001946154079632834</v>
+        <v>0.0002817573840729892</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0001341112074442208</v>
+        <v>0.0002138637792086229</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.001125967944972217</v>
+        <v>0.0001859267358668149</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.002935915254056454</v>
+        <v>0.002017449820414186</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.00118559633847326</v>
+        <v>0.0008561342256143689</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0034817298874259</v>
+        <v>0.001593345543369651</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.0006843950832262635</v>
+        <v>0.0001604863500688225</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.001018845243379474</v>
+        <v>0.003721736371517181</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.001451353658922017</v>
+        <v>0.0008809579885564744</v>
       </c>
       <c r="DL10" t="n">
-        <v>3.726697468664497e-05</v>
+        <v>0.003452119650319219</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.001062420546077192</v>
+        <v>0.001309018931351602</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.002818512264639139</v>
+        <v>0.0004052832955494523</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.001122866058722138</v>
+        <v>0.001004049554467201</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.001779495854862034</v>
+        <v>0.0002541386929806322</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.000625324435532093</v>
+        <v>0.0005693627754226327</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.001132724806666374</v>
+        <v>4.178038216196001e-05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.002199138980358839</v>
+        <v>0.0007529315771535039</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.0008382681990042329</v>
+        <v>0.0007796590798534453</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.0003463001048658043</v>
+        <v>0.001400203676894307</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.0003678264329209924</v>
+        <v>0.002789223100990057</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0007144702249206603</v>
+        <v>6.578589091077447e-05</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0001266423787456006</v>
+        <v>2.684045466594398e-05</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.001618771464563906</v>
+        <v>0.001142175286076963</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.001303261611610651</v>
+        <v>0.0008342799264937639</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.002822150243446231</v>
+        <v>9.636460163164884e-05</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.002055444288998842</v>
+        <v>0.00175972527358681</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0005441689863801003</v>
+        <v>0.0001484773092670366</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.000726501049939543</v>
+        <v>0.00322065083310008</v>
       </c>
       <c r="EE10" t="n">
-        <v>4.051790165249258e-05</v>
+        <v>0.003250178880989552</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.001062408788129687</v>
+        <v>0.001014205859974027</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.001831132220104337</v>
+        <v>0.001295093214139342</v>
       </c>
       <c r="EH10" t="n">
-        <v>9.738221706356853e-06</v>
+        <v>0.001172863878309727</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.001859853626228869</v>
+        <v>0.001960590947419405</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.001041740062646568</v>
+        <v>0.0001555698254378513</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.001062257448211312</v>
+        <v>0.0006238524802029133</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.000751904328353703</v>
+        <v>9.189224510919303e-05</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0005706134834326804</v>
+        <v>0.0002068719622911885</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0001630708575248718</v>
+        <v>0.0002290272677782923</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.001349023194052279</v>
+        <v>0.0007375919376499951</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.002162215765565634</v>
+        <v>0.002063368214294314</v>
       </c>
       <c r="EQ10" t="n">
-        <v>6.813908112235367e-05</v>
+        <v>0.0001259825075976551</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.001811959082260728</v>
+        <v>0.001657268148846924</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0007467598188668489</v>
+        <v>0.0003967233060393482</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.005578749813139439</v>
+        <v>0.0003101166803389788</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.001547901309095323</v>
+        <v>0.0006975766737014055</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.00131277262698859</v>
+        <v>0.0007337501738220453</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.0001329598453594372</v>
+        <v>0.001610019360668957</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0008998973062261939</v>
+        <v>3.837991243926808e-05</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.002738298382610083</v>
+        <v>0.002125154482200742</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.000479834561701864</v>
+        <v>0.0002111385983880609</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.001564406557008624</v>
+        <v>0.002339282538741827</v>
       </c>
       <c r="FB10" t="n">
-        <v>6.702854443574324e-05</v>
+        <v>6.000367648084648e-06</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.001572338631376624</v>
+        <v>0.0007949834107421339</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0009199137566611171</v>
+        <v>0.0004222416318953037</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0001757914287736639</v>
+        <v>0.0005166781484149396</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0003060469753108919</v>
+        <v>0.0004951126757077873</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.0006272941245697439</v>
+        <v>0.0002101840364048257</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.001117876381613314</v>
+        <v>0.0009483775938861072</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0001906368706841022</v>
+        <v>0.0002054010546999052</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.001976384548470378</v>
+        <v>0.001260091783478856</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.001287343329750001</v>
+        <v>0.000581778003834188</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.001034371205605567</v>
+        <v>0.0001840973854996264</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.000946330779697746</v>
+        <v>0.0006534955464303493</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0002694278955459595</v>
+        <v>6.021145964041352e-05</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0007626731530763209</v>
+        <v>0.0004305673646740615</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0002150023356080055</v>
+        <v>0.0009714901680126786</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0001888435072032735</v>
+        <v>0.002489301608875394</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.0004478039045352489</v>
+        <v>0.001521524041891098</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.003169470466673374</v>
+        <v>0.002124054124578834</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0009388945763930678</v>
+        <v>0.002141083125025034</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0001782123290468007</v>
+        <v>0.001305746613070369</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.0007152807665988803</v>
+        <v>0.0002497954701539129</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.0002514588704798371</v>
+        <v>0.002604197710752487</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0009511965909041464</v>
+        <v>0.001540495664812624</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.002310254611074924</v>
+        <v>0.0008505892474204302</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.001745179179124534</v>
+        <v>0.0001002467470243573</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.0004645686713047326</v>
+        <v>0.0008029446471482515</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0008321316563524306</v>
+        <v>0.002099706092849374</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0004122895770706236</v>
+        <v>0.0002394752227701247</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.002830590819939971</v>
+        <v>0.001265600207261741</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.004190347157418728</v>
+        <v>0.001354266423732042</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.0005985914613120258</v>
+        <v>0.0009208109113387764</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0009157205931842327</v>
+        <v>0.0008665906498208642</v>
       </c>
     </row>
     <row r="11">
@@ -6689,1709 +6689,1709 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5.886474419014576e-09</v>
+        <v>1.790221082487164e-09</v>
       </c>
       <c r="B12" t="n">
-        <v>2.427407963523365e-08</v>
+        <v>1.590219333991172e-08</v>
       </c>
       <c r="C12" t="n">
-        <v>2.688503641934403e-09</v>
+        <v>3.194603914735694e-09</v>
       </c>
       <c r="D12" t="n">
-        <v>4.996211799834782e-08</v>
+        <v>2.358532258384116e-09</v>
       </c>
       <c r="E12" t="n">
-        <v>4.91219775966556e-09</v>
+        <v>5.134019431807246e-09</v>
       </c>
       <c r="F12" t="n">
-        <v>1.511202829540537e-09</v>
+        <v>7.304136850905252e-09</v>
       </c>
       <c r="G12" t="n">
-        <v>3.957831395950961e-09</v>
+        <v>3.237389689658698e-09</v>
       </c>
       <c r="H12" t="n">
-        <v>1.237271840537346e-09</v>
+        <v>5.005007519542914e-09</v>
       </c>
       <c r="I12" t="n">
-        <v>2.369998641782445e-10</v>
+        <v>2.145241539963649e-09</v>
       </c>
       <c r="J12" t="n">
-        <v>1.174884367571849e-08</v>
+        <v>1.071336352964636e-09</v>
       </c>
       <c r="K12" t="n">
-        <v>1.412451666737979e-08</v>
+        <v>1.890124323722375e-08</v>
       </c>
       <c r="L12" t="n">
-        <v>9.922688226637888e-10</v>
+        <v>5.188172558234783e-09</v>
       </c>
       <c r="M12" t="n">
-        <v>2.784212327355817e-08</v>
+        <v>6.364218485543915e-09</v>
       </c>
       <c r="N12" t="n">
-        <v>1.107849278980666e-08</v>
+        <v>1.027053109226017e-08</v>
       </c>
       <c r="O12" t="n">
-        <v>1.135213967273785e-08</v>
+        <v>7.73428787681496e-09</v>
       </c>
       <c r="P12" t="n">
-        <v>8.881625213064126e-09</v>
+        <v>1.113532488439262e-09</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.222046996929294e-08</v>
+        <v>1.882851652368345e-10</v>
       </c>
       <c r="R12" t="n">
-        <v>2.165490009531368e-11</v>
+        <v>5.972519367958284e-09</v>
       </c>
       <c r="S12" t="n">
-        <v>2.800442988615259e-09</v>
+        <v>1.397226445654098e-09</v>
       </c>
       <c r="T12" t="n">
-        <v>3.920195279505378e-09</v>
+        <v>6.740021873952173e-10</v>
       </c>
       <c r="U12" t="n">
-        <v>4.912016571267941e-09</v>
+        <v>2.703220314259625e-09</v>
       </c>
       <c r="V12" t="n">
-        <v>3.886782895534679e-09</v>
+        <v>9.244803256258649e-10</v>
       </c>
       <c r="W12" t="n">
-        <v>5.517306167490688e-09</v>
+        <v>1.723203690850994e-09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.952123129811412e-09</v>
+        <v>2.621549421988334e-09</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.557145523634063e-08</v>
+        <v>2.227110496022533e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.613748772972713e-09</v>
+        <v>6.260523210954716e-10</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.696204923883897e-09</v>
+        <v>2.731208148532005e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.625518386560998e-09</v>
+        <v>5.725118157329234e-10</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.489078749195016e-09</v>
+        <v>3.298306516796856e-09</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.287201539274974e-10</v>
+        <v>1.275251904075958e-09</v>
       </c>
       <c r="AE12" t="n">
-        <v>5.459625640469312e-09</v>
+        <v>3.522936831146239e-09</v>
       </c>
       <c r="AF12" t="n">
-        <v>7.877260621569349e-09</v>
+        <v>5.993974205864561e-09</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.537534430999358e-09</v>
+        <v>9.593261296458877e-09</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.561739347901494e-09</v>
+        <v>3.266988068961751e-10</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.454398462248264e-09</v>
+        <v>7.833737214468783e-09</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9.593531524743071e-10</v>
+        <v>8.702872311694421e-10</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.692811612054925e-09</v>
+        <v>4.267753928033358e-10</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.532177300120566e-09</v>
+        <v>3.564894157648268e-09</v>
       </c>
       <c r="AM12" t="n">
-        <v>2.057950032607891e-09</v>
+        <v>3.790215696852783e-09</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.28312746486381e-09</v>
+        <v>9.601974770845345e-11</v>
       </c>
       <c r="AO12" t="n">
-        <v>2.205787330566977e-09</v>
+        <v>8.221789915552336e-10</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.105218526755493e-09</v>
+        <v>3.398960224387793e-09</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.400651925668853e-09</v>
+        <v>1.660093063016177e-09</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.618216754513014e-09</v>
+        <v>5.642073475087273e-10</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.695072330918038e-09</v>
+        <v>6.860972900923912e-11</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.027842255751921e-09</v>
+        <v>1.322948195436879e-09</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.379811376267526e-08</v>
+        <v>1.42282843285102e-08</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.736530919060897e-09</v>
+        <v>5.270265113210826e-09</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.242380681138911e-08</v>
+        <v>2.510833096991405e-09</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.655917181153654e-09</v>
+        <v>1.009625449910345e-08</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.425235733407362e-09</v>
+        <v>9.367314035557683e-09</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.344510363627705e-09</v>
+        <v>9.907730191827113e-11</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.706513540535639e-09</v>
+        <v>1.697633034147827e-09</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.055068299393724e-08</v>
+        <v>1.981417252494566e-09</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.280845373154762e-09</v>
+        <v>2.074960647746593e-09</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.182390155373696e-10</v>
+        <v>6.126629203961897e-10</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.301277556351124e-09</v>
+        <v>3.854708552353259e-09</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.65851668352002e-09</v>
+        <v>2.164144641270127e-09</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.384562377727889e-09</v>
+        <v>6.308241928820735e-09</v>
       </c>
       <c r="BH12" t="n">
-        <v>5.482507781096047e-09</v>
+        <v>2.842834856409127e-10</v>
       </c>
       <c r="BI12" t="n">
-        <v>8.719981181570802e-09</v>
+        <v>1.391809167916591e-10</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.756530565444336e-08</v>
+        <v>5.698810312537717e-09</v>
       </c>
       <c r="BK12" t="n">
-        <v>2.685849320727129e-10</v>
+        <v>2.775574436952866e-09</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.447533204412821e-09</v>
+        <v>4.327760372291323e-12</v>
       </c>
       <c r="BM12" t="n">
-        <v>3.842418605515263e-10</v>
+        <v>4.430388056420043e-09</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.208760534003432e-09</v>
+        <v>1.481832989647103e-09</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.877812376236079e-09</v>
+        <v>3.271814486005553e-10</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.282506793629182e-09</v>
+        <v>6.119381890101749e-09</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.612972143685056e-09</v>
+        <v>2.297083412372558e-09</v>
       </c>
       <c r="BR12" t="n">
-        <v>3.19845039342681e-09</v>
+        <v>2.979800850511083e-09</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.682150863047127e-09</v>
+        <v>3.362323752753582e-09</v>
       </c>
       <c r="BT12" t="n">
-        <v>5.216868048663059e-10</v>
+        <v>2.075926097688807e-10</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.921141468130827e-09</v>
+        <v>1.187143383596378e-09</v>
       </c>
       <c r="BV12" t="n">
-        <v>7.853217631748066e-09</v>
+        <v>8.012657204403695e-09</v>
       </c>
       <c r="BW12" t="n">
-        <v>3.310230090036725e-09</v>
+        <v>3.233476153496895e-09</v>
       </c>
       <c r="BX12" t="n">
-        <v>9.577272308547435e-09</v>
+        <v>2.592041026261427e-10</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.406132069258774e-09</v>
+        <v>2.305914126310427e-09</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.943736365779159e-09</v>
+        <v>6.251035244986269e-09</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.704082622377427e-09</v>
+        <v>3.240737900256363e-09</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.431750522115863e-09</v>
+        <v>2.487292594111068e-09</v>
       </c>
       <c r="CC12" t="n">
-        <v>7.548547564795172e-09</v>
+        <v>3.256984681954123e-09</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.393162583189337e-10</v>
+        <v>1.248175729440248e-10</v>
       </c>
       <c r="CE12" t="n">
-        <v>4.287087129739575e-09</v>
+        <v>5.676566328105537e-09</v>
       </c>
       <c r="CF12" t="n">
-        <v>5.56711787780273e-09</v>
+        <v>2.221550721159815e-11</v>
       </c>
       <c r="CG12" t="n">
-        <v>5.015961868082286e-09</v>
+        <v>5.688868265352198e-10</v>
       </c>
       <c r="CH12" t="n">
-        <v>2.104108887124312e-09</v>
+        <v>2.143607735760611e-09</v>
       </c>
       <c r="CI12" t="n">
-        <v>3.484689758970205e-10</v>
+        <v>3.220567590389578e-09</v>
       </c>
       <c r="CJ12" t="n">
-        <v>3.51470164083878e-09</v>
+        <v>1.231598156792302e-11</v>
       </c>
       <c r="CK12" t="n">
-        <v>2.264127552109585e-09</v>
+        <v>4.063709091450818e-11</v>
       </c>
       <c r="CL12" t="n">
-        <v>5.180139428517805e-09</v>
+        <v>2.671290133537951e-10</v>
       </c>
       <c r="CM12" t="n">
-        <v>6.469228708283481e-09</v>
+        <v>4.309933743229521e-09</v>
       </c>
       <c r="CN12" t="n">
-        <v>5.899502664163947e-09</v>
+        <v>8.433501896831785e-09</v>
       </c>
       <c r="CO12" t="n">
-        <v>2.683777089451667e-10</v>
+        <v>8.718873623081436e-09</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.038662666985601e-08</v>
+        <v>2.899967821434757e-09</v>
       </c>
       <c r="CQ12" t="n">
-        <v>4.830112754206084e-09</v>
+        <v>2.501452378567137e-09</v>
       </c>
       <c r="CR12" t="n">
-        <v>3.519101232640764e-09</v>
+        <v>6.113507033944643e-09</v>
       </c>
       <c r="CS12" t="n">
-        <v>5.945621772696086e-09</v>
+        <v>1.688235884422795e-09</v>
       </c>
       <c r="CT12" t="n">
-        <v>1.555490314331109e-08</v>
+        <v>3.706489004606794e-10</v>
       </c>
       <c r="CU12" t="n">
-        <v>3.875417764476197e-09</v>
+        <v>6.851696987553169e-11</v>
       </c>
       <c r="CV12" t="n">
-        <v>8.714244326135656e-10</v>
+        <v>5.606684561065833e-10</v>
       </c>
       <c r="CW12" t="n">
-        <v>4.197554748230914e-09</v>
+        <v>5.251490353685995e-09</v>
       </c>
       <c r="CX12" t="n">
-        <v>4.707919831759e-09</v>
+        <v>6.513044548128732e-10</v>
       </c>
       <c r="CY12" t="n">
-        <v>8.631222847554909e-09</v>
+        <v>1.165312402129359e-09</v>
       </c>
       <c r="CZ12" t="n">
-        <v>3.091716882508422e-09</v>
+        <v>2.827065914701166e-09</v>
       </c>
       <c r="DA12" t="n">
-        <v>7.64040664069654e-10</v>
+        <v>2.930311104876182e-09</v>
       </c>
       <c r="DB12" t="n">
-        <v>3.019586136687735e-09</v>
+        <v>5.373367861771783e-10</v>
       </c>
       <c r="DC12" t="n">
-        <v>3.032645912171006e-09</v>
+        <v>2.127711479227301e-10</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.904747192251534e-09</v>
+        <v>9.914250531650737e-10</v>
       </c>
       <c r="DE12" t="n">
-        <v>5.273978143094382e-09</v>
+        <v>5.917288881107652e-11</v>
       </c>
       <c r="DF12" t="n">
-        <v>5.938478153666438e-09</v>
+        <v>1.35179356597348e-09</v>
       </c>
       <c r="DG12" t="n">
-        <v>7.982484007129642e-09</v>
+        <v>6.579223832403613e-10</v>
       </c>
       <c r="DH12" t="n">
-        <v>3.406102777603337e-08</v>
+        <v>1.351344258715415e-09</v>
       </c>
       <c r="DI12" t="n">
-        <v>1.253278192336893e-08</v>
+        <v>6.931051288461276e-10</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.245844760688897e-09</v>
+        <v>8.579974952738212e-09</v>
       </c>
       <c r="DK12" t="n">
-        <v>8.05398858716444e-09</v>
+        <v>1.416457839908958e-09</v>
       </c>
       <c r="DL12" t="n">
-        <v>1.823220507901624e-08</v>
+        <v>4.379538509624581e-09</v>
       </c>
       <c r="DM12" t="n">
-        <v>2.212253491506999e-09</v>
+        <v>3.366385614711476e-09</v>
       </c>
       <c r="DN12" t="n">
-        <v>4.090432437209301e-10</v>
+        <v>1.878450284209521e-09</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.514513708362642e-09</v>
+        <v>3.45014905533958e-09</v>
       </c>
       <c r="DP12" t="n">
-        <v>7.74462538544185e-09</v>
+        <v>1.878403876887091e-09</v>
       </c>
       <c r="DQ12" t="n">
-        <v>4.209546489164495e-09</v>
+        <v>2.312704916462849e-09</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.580039541541737e-09</v>
+        <v>9.230044506480795e-11</v>
       </c>
       <c r="DS12" t="n">
-        <v>5.200005759320447e-09</v>
+        <v>1.776958580279597e-09</v>
       </c>
       <c r="DT12" t="n">
-        <v>1.05786113202555e-09</v>
+        <v>1.658392534409359e-09</v>
       </c>
       <c r="DU12" t="n">
-        <v>9.119686117387005e-10</v>
+        <v>1.79507064768103e-09</v>
       </c>
       <c r="DV12" t="n">
-        <v>8.615774760301065e-09</v>
+        <v>1.49057888254589e-09</v>
       </c>
       <c r="DW12" t="n">
-        <v>1.008301886429308e-09</v>
+        <v>2.998344905691397e-10</v>
       </c>
       <c r="DX12" t="n">
-        <v>4.754535876116961e-09</v>
+        <v>1.163588447816721e-09</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.445670746619726e-09</v>
+        <v>2.524704889594886e-09</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.216976462994126e-09</v>
+        <v>6.87901624552012e-10</v>
       </c>
       <c r="EA12" t="n">
-        <v>8.506043869260793e-09</v>
+        <v>3.626231759312759e-09</v>
       </c>
       <c r="EB12" t="n">
-        <v>7.86689113851935e-09</v>
+        <v>3.134398518511716e-09</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.730080662065703e-10</v>
+        <v>1.20404353154413e-09</v>
       </c>
       <c r="ED12" t="n">
-        <v>4.462840763608256e-09</v>
+        <v>5.331046271095374e-09</v>
       </c>
       <c r="EE12" t="n">
-        <v>1.056260745535553e-09</v>
+        <v>7.148224234754252e-09</v>
       </c>
       <c r="EF12" t="n">
-        <v>7.281611980047842e-10</v>
+        <v>1.910377411817876e-10</v>
       </c>
       <c r="EG12" t="n">
-        <v>2.026978807023738e-09</v>
+        <v>1.356019629916716e-09</v>
       </c>
       <c r="EH12" t="n">
-        <v>4.106351259025587e-09</v>
+        <v>3.227176303965962e-09</v>
       </c>
       <c r="EI12" t="n">
-        <v>6.340271863081171e-09</v>
+        <v>2.278799149380006e-09</v>
       </c>
       <c r="EJ12" t="n">
-        <v>4.084910187884816e-09</v>
+        <v>1.294847118415987e-09</v>
       </c>
       <c r="EK12" t="n">
-        <v>1.693908457944815e-09</v>
+        <v>2.976978663582486e-09</v>
       </c>
       <c r="EL12" t="n">
-        <v>4.917791063263621e-09</v>
+        <v>8.402621931580256e-10</v>
       </c>
       <c r="EM12" t="n">
-        <v>1.256904358371003e-09</v>
+        <v>4.331831005011111e-10</v>
       </c>
       <c r="EN12" t="n">
-        <v>2.769130924562546e-09</v>
+        <v>3.599861742031862e-09</v>
       </c>
       <c r="EO12" t="n">
-        <v>8.67330152143353e-10</v>
+        <v>4.775766448972263e-10</v>
       </c>
       <c r="EP12" t="n">
-        <v>1.148833250752546e-09</v>
+        <v>4.880480908298068e-09</v>
       </c>
       <c r="EQ12" t="n">
-        <v>4.241123008341674e-09</v>
+        <v>1.089059287195937e-09</v>
       </c>
       <c r="ER12" t="n">
-        <v>3.338386678208849e-09</v>
+        <v>5.096862376596789e-10</v>
       </c>
       <c r="ES12" t="n">
-        <v>1.47024019625519e-08</v>
+        <v>4.658012309199933e-10</v>
       </c>
       <c r="ET12" t="n">
-        <v>2.61873278617486e-09</v>
+        <v>2.93621083002904e-09</v>
       </c>
       <c r="EU12" t="n">
-        <v>3.176647833669222e-09</v>
+        <v>3.096614631381556e-11</v>
       </c>
       <c r="EV12" t="n">
-        <v>8.563386444393473e-09</v>
+        <v>1.329959697926597e-09</v>
       </c>
       <c r="EW12" t="n">
-        <v>2.865974124688364e-10</v>
+        <v>2.834588341826816e-09</v>
       </c>
       <c r="EX12" t="n">
-        <v>7.214233654906366e-10</v>
+        <v>1.850182507201481e-10</v>
       </c>
       <c r="EY12" t="n">
-        <v>3.930984870947896e-09</v>
+        <v>6.240082228714527e-09</v>
       </c>
       <c r="EZ12" t="n">
-        <v>4.899809002978373e-09</v>
+        <v>4.324383073850413e-10</v>
       </c>
       <c r="FA12" t="n">
-        <v>7.77445219313222e-09</v>
+        <v>1.242333791395822e-09</v>
       </c>
       <c r="FB12" t="n">
-        <v>1.78192660627019e-09</v>
+        <v>1.411206040913271e-09</v>
       </c>
       <c r="FC12" t="n">
-        <v>4.438564793485256e-10</v>
+        <v>3.011050964119022e-09</v>
       </c>
       <c r="FD12" t="n">
-        <v>3.846415186359309e-09</v>
+        <v>5.409893644170438e-10</v>
       </c>
       <c r="FE12" t="n">
-        <v>3.00773939088117e-09</v>
+        <v>6.372236072138548e-10</v>
       </c>
       <c r="FF12" t="n">
-        <v>5.666183078290032e-09</v>
+        <v>2.038784918667602e-09</v>
       </c>
       <c r="FG12" t="n">
-        <v>1.359626855546026e-09</v>
+        <v>1.677494032570337e-09</v>
       </c>
       <c r="FH12" t="n">
-        <v>3.608923826448063e-09</v>
+        <v>2.794708908737675e-09</v>
       </c>
       <c r="FI12" t="n">
-        <v>9.106507548040099e-09</v>
+        <v>1.54381063488529e-09</v>
       </c>
       <c r="FJ12" t="n">
-        <v>1.385685610699738e-08</v>
+        <v>2.452553271581337e-09</v>
       </c>
       <c r="FK12" t="n">
-        <v>3.955475502692707e-09</v>
+        <v>9.97374516309435e-10</v>
       </c>
       <c r="FL12" t="n">
-        <v>1.541412775196704e-09</v>
+        <v>1.710686703404463e-09</v>
       </c>
       <c r="FM12" t="n">
-        <v>6.4223457663104e-09</v>
+        <v>1.00063302088671e-09</v>
       </c>
       <c r="FN12" t="n">
-        <v>3.522737879180227e-09</v>
+        <v>3.73232111883226e-10</v>
       </c>
       <c r="FO12" t="n">
-        <v>2.174717961267447e-09</v>
+        <v>7.149914438286942e-09</v>
       </c>
       <c r="FP12" t="n">
-        <v>5.048709894595049e-09</v>
+        <v>2.819523725605677e-09</v>
       </c>
       <c r="FQ12" t="n">
-        <v>2.091506079437977e-09</v>
+        <v>5.318606888238264e-09</v>
       </c>
       <c r="FR12" t="n">
-        <v>3.271014348271706e-09</v>
+        <v>4.33387015164044e-09</v>
       </c>
       <c r="FS12" t="n">
-        <v>1.163404372839238e-09</v>
+        <v>1.504017133058255e-09</v>
       </c>
       <c r="FT12" t="n">
-        <v>9.541462731021966e-09</v>
+        <v>4.28138724473115e-09</v>
       </c>
       <c r="FU12" t="n">
-        <v>1.869946419930102e-09</v>
+        <v>2.434500157022512e-09</v>
       </c>
       <c r="FV12" t="n">
-        <v>2.465967430254068e-09</v>
+        <v>2.347443128769555e-09</v>
       </c>
       <c r="FW12" t="n">
-        <v>4.91776619426787e-09</v>
+        <v>5.389832580249276e-09</v>
       </c>
       <c r="FX12" t="n">
-        <v>2.729881876106788e-09</v>
+        <v>1.132824112293207e-10</v>
       </c>
       <c r="FY12" t="n">
-        <v>9.656273114444502e-09</v>
+        <v>1.450675801706325e-09</v>
       </c>
       <c r="FZ12" t="n">
-        <v>2.773683061008114e-09</v>
+        <v>6.609904290577617e-10</v>
       </c>
       <c r="GA12" t="n">
-        <v>1.847800801257904e-09</v>
+        <v>1.902956014987467e-09</v>
       </c>
       <c r="GB12" t="n">
-        <v>2.018410771853496e-09</v>
+        <v>2.146831379334913e-09</v>
       </c>
       <c r="GC12" t="n">
-        <v>7.727322781647672e-09</v>
+        <v>2.015404954036626e-09</v>
       </c>
       <c r="GD12" t="n">
-        <v>4.690748900415542e-10</v>
+        <v>6.534271346225751e-09</v>
       </c>
       <c r="GE12" t="n">
-        <v>2.064176918281646e-08</v>
+        <v>3.101261469851124e-09</v>
       </c>
       <c r="GF12" t="n">
-        <v>7.358758602471482e-10</v>
+        <v>1.277728145510082e-09</v>
       </c>
       <c r="GG12" t="n">
-        <v>6.308773503604925e-09</v>
+        <v>3.090457889598497e-09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.002339448314160109</v>
+        <v>0.0001435286831110716</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01324947830289602</v>
+        <v>0.003325040452182293</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0004713630769401789</v>
+        <v>0.001484639244154096</v>
       </c>
       <c r="D13" t="n">
-        <v>0.007409997750073671</v>
+        <v>0.0006910617812536657</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001218255376443267</v>
+        <v>0.003160055028274655</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01147095300257206</v>
+        <v>0.003376622684299946</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0002621877938508987</v>
+        <v>0.0009831939823925495</v>
       </c>
       <c r="H13" t="n">
-        <v>0.002235277788713574</v>
+        <v>0.004302046727389097</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0001213700306834653</v>
+        <v>0.0009734277846291661</v>
       </c>
       <c r="J13" t="n">
-        <v>0.003159842686727643</v>
+        <v>0.0009886733023449779</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01005280949175358</v>
+        <v>0.009031270630657673</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0004951914306730032</v>
+        <v>0.0005409924779087305</v>
       </c>
       <c r="M13" t="n">
-        <v>0.008105975575745106</v>
+        <v>0.001323726959526539</v>
       </c>
       <c r="N13" t="n">
-        <v>0.002842256333678961</v>
+        <v>0.004134866409003735</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01284898724406958</v>
+        <v>0.004579962231218815</v>
       </c>
       <c r="P13" t="n">
-        <v>0.001394359394907951</v>
+        <v>0.003446210408583283</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.860452514141798e-05</v>
+        <v>0.0005420968518592417</v>
       </c>
       <c r="R13" t="n">
-        <v>9.304983541369438e-05</v>
+        <v>5.31814293935895e-06</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0006098994635976851</v>
+        <v>0.0005002724938094616</v>
       </c>
       <c r="T13" t="n">
-        <v>0.002202355302870274</v>
+        <v>2.312392462044954e-05</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0003166247333865613</v>
+        <v>0.0006416909163817763</v>
       </c>
       <c r="V13" t="n">
-        <v>0.002024220768362284</v>
+        <v>0.00195803539827466</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0009941569296643138</v>
+        <v>0.002859960310161114</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0002068176254397258</v>
+        <v>0.0004425307852216065</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.001429760130122304</v>
+        <v>0.0005032638437114656</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0001526607666164637</v>
+        <v>0.002094031311571598</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.001817517215386033</v>
+        <v>0.000483679526951164</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0003598852781578898</v>
+        <v>0.0020369125995785</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.00186152895912528</v>
+        <v>0.0005201438325457275</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0002154166140826419</v>
+        <v>0.0002677143784239888</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.001295393332839012</v>
+        <v>0.0008794485474936664</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0009113157284446061</v>
+        <v>0.001264089718461037</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.0002117042895406485</v>
+        <v>0.0003008691128343344</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.002515713684260845</v>
+        <v>0.001936574117280543</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0002415923518128693</v>
+        <v>0.004983673803508282</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0001113082398660481</v>
+        <v>0.0007402326446026564</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.001656495616771281</v>
+        <v>0.0008990369969978929</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.001856420072726905</v>
+        <v>0.000780050759203732</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0003765206784009933</v>
+        <v>0.0003578508039936423</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0009991433471441269</v>
+        <v>0.0009946983773261309</v>
       </c>
       <c r="AO13" t="n">
-        <v>9.318403317593038e-05</v>
+        <v>0.00236256024800241</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.001821799785830081</v>
+        <v>0.0001861047057900578</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.001024744124151766</v>
+        <v>0.000195985398022458</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.0002106400788761675</v>
+        <v>0.002518791472539306</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.001376435626298189</v>
+        <v>0.0005433047190308571</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.002042388543486595</v>
+        <v>0.00024550044327043</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.01104505732655525</v>
+        <v>0.007931701838970184</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0009953533299267292</v>
+        <v>0.001424011075869203</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0006132160197012126</v>
+        <v>0.0001810754329198971</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.001945706433616579</v>
+        <v>0.002441641874611378</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.006145332474261522</v>
+        <v>0.002886621048673987</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0008183707832358778</v>
+        <v>0.0001655841188039631</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.002982445526868105</v>
+        <v>0.00066852115560323</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.002351784147322178</v>
+        <v>0.0003515960124786943</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.001538911485113204</v>
+        <v>0.0001491106231696904</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.002324051922187209</v>
+        <v>0.001039627473801374</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.00356016238220036</v>
+        <v>0.001217957818880677</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.003779046470299363</v>
+        <v>0.003752881195396185</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.004686227068305016</v>
+        <v>0.002117308788001537</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.004250488243997097</v>
+        <v>0.000334360491251573</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.736939445137978e-06</v>
+        <v>0.0009677155176177621</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.003847677959129214</v>
+        <v>0.005005375016480684</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0001696325489319861</v>
+        <v>0.001461580977775156</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0005722495261579752</v>
+        <v>0.0003507009823806584</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.003793088719248772</v>
+        <v>0.004130063112825155</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0009266792912967503</v>
+        <v>0.0008070236071944237</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.003711505560204387</v>
+        <v>0.002482792595401406</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.002891228534281254</v>
+        <v>0.003353302599862218</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0002300698251929134</v>
+        <v>0.0002693936112336814</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.002177202608436346</v>
+        <v>0.0008086115121841431</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0002612877869978547</v>
+        <v>0.003084781812503934</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0001881865318864584</v>
+        <v>0.0001023098157020286</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0007911266293376684</v>
+        <v>0.0007788539514876902</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.005076820030808449</v>
+        <v>0.003629830665886402</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0003932924009859562</v>
+        <v>0.0008793091401457787</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0006855757674202323</v>
+        <v>0.001961769536137581</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.000931857037357986</v>
+        <v>0.001869850209914148</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.001428581192158163</v>
+        <v>0.0006211075815372169</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.002561792731285095</v>
+        <v>0.0007471386925317347</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.001522486098110676</v>
+        <v>0.001145418267697096</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.001302328077144921</v>
+        <v>0.0002188732614740729</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0003511683898977935</v>
+        <v>0.0005614609690383077</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.002499798545613885</v>
+        <v>0.001224929234012961</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.00128303375095129</v>
+        <v>0.0002134783135261387</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.001272862078621984</v>
+        <v>0.0003552244161255658</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0008402077946811914</v>
+        <v>0.0009439992718398571</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.00210220692679286</v>
+        <v>0.001123785157687962</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0003886496997438371</v>
+        <v>0.0001370570389553905</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0003871042281389236</v>
+        <v>7.258264668053016e-05</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0007296062540262938</v>
+        <v>5.597118797595613e-05</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.00228207721374929</v>
+        <v>0.001069664722308517</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.002071177354082465</v>
+        <v>0.004284422378987074</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.0003597473551053554</v>
+        <v>0.001006916165351868</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.001758316648192704</v>
+        <v>0.004978274460881948</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0003262071113567799</v>
+        <v>0.001396699226461351</v>
       </c>
       <c r="CR13" t="n">
-        <v>3.88886546716094e-05</v>
+        <v>0.0005790787981823087</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0004152142500970513</v>
+        <v>0.00110604939982295</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.001563591882586479</v>
+        <v>0.001524476916529238</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.000827253214083612</v>
+        <v>0.0002552421647123992</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0001536313066026196</v>
+        <v>0.0002159907890018076</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.001753312419168651</v>
+        <v>0.001047434168867767</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.001193805946968496</v>
+        <v>7.449563418049365e-05</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.002087286440655589</v>
+        <v>0.0009204965317621827</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0005725057562813163</v>
+        <v>0.0004045483656227589</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.001882418058812618</v>
+        <v>0.001155950711108744</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0007324718753807247</v>
+        <v>0.0003957950393669307</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.001434374251402915</v>
+        <v>0.0001679060369497165</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.000310327741317451</v>
+        <v>0.0003042401513084769</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.00176464777905494</v>
+        <v>0.001227421569637954</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.004626802634447813</v>
+        <v>0.0009806721936911345</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.0006689446745440364</v>
+        <v>0.003551754634827375</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.00358659983612597</v>
+        <v>0.001664243172854185</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0009677037596702576</v>
+        <v>0.002251191530376673</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.001472090021707118</v>
+        <v>0.0005180175066925585</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.002888407092541456</v>
+        <v>0.0003245479892939329</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.00261563784442842</v>
+        <v>0.000144854246173054</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.001786521752364933</v>
+        <v>3.509398084133863e-06</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.001442480832338333</v>
+        <v>0.0006175432354211807</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.001433334429748356</v>
+        <v>0.002204929012805223</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.001703161746263504</v>
+        <v>0.0003905662742909044</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.002063930965960026</v>
+        <v>0.0009564298670738935</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0009295077761635184</v>
+        <v>0.0007335174595937133</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0003756274236366153</v>
+        <v>9.239772771252319e-05</v>
       </c>
       <c r="DT13" t="n">
-        <v>9.325658902525902e-05</v>
+        <v>0.0003963311901316047</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0005091056227684021</v>
+        <v>0.00376237416639924</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0003398332046344876</v>
+        <v>0.0002111342473654076</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0003400696441531181</v>
+        <v>0.001704524969682097</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.0001263583544641733</v>
+        <v>0.00150998798198998</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.001921932445839047</v>
+        <v>0.001242739846929908</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0006619727937504649</v>
+        <v>0.0004019812622573227</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.001000136602669954</v>
+        <v>0.0006654594326391816</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0003380926209501922</v>
+        <v>1.998155858018436e-05</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0002690849942155182</v>
+        <v>0.001666525728069246</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0007447565440088511</v>
+        <v>0.002275458071380854</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0008495663059875369</v>
+        <v>0.002134292153641582</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0008211224339902401</v>
+        <v>0.0006394832162186503</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0002816527849063277</v>
+        <v>0.0005357997724786401</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0002521033748053014</v>
+        <v>0.0001406591618433595</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0005052445339970291</v>
+        <v>0.0003431371878832579</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0001994746562559158</v>
+        <v>0.0002418102812953293</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.00118557270616293</v>
+        <v>0.001550899818539619</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.001190102659165859</v>
+        <v>0.0001183810963993892</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0001775790587998927</v>
+        <v>0.0009289409499615431</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0003935864951927215</v>
+        <v>0.0003654971369542181</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.001419418957084417</v>
+        <v>0.000650470785330981</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0005369522259570658</v>
+        <v>0.0001118547806981951</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0007880227640271187</v>
+        <v>8.647341746836901e-05</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0006897905841469765</v>
+        <v>4.591127799358219e-05</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0009385601151734591</v>
+        <v>0.001126810209825635</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.002556760562583804</v>
+        <v>0.001040332135744393</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0009599638869985938</v>
+        <v>0.001124094356782734</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.002122589619830251</v>
+        <v>0.0006564372451975942</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.000267568597337231</v>
+        <v>0.0005775117315351963</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0002977725234813988</v>
+        <v>0.0003872364468406886</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.001577376970089972</v>
+        <v>0.001538487616926432</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0007459222106263041</v>
+        <v>0.0003347785677760839</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.00125854997895658</v>
+        <v>0.0008846694836392999</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0006486966158263385</v>
+        <v>0.0004755682602990419</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.00186745950486511</v>
+        <v>0.001415845821611583</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0009025099570862949</v>
+        <v>4.144613922107965e-05</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0005299338372424245</v>
+        <v>0.0003045252524316311</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0009255922632291913</v>
+        <v>0.000312788353767246</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0008047763840295374</v>
+        <v>0.0009793626377359033</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.001433453406207263</v>
+        <v>0.0009940963936969638</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.001184418681077659</v>
+        <v>3.391917562112212e-05</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0002294120495207608</v>
+        <v>0.002180314157158136</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0001049241400323808</v>
+        <v>0.001362121431156993</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0009277775534428656</v>
+        <v>0.00113790319301188</v>
       </c>
       <c r="FM13" t="n">
-        <v>5.123869050294161e-05</v>
+        <v>0.001147286966443062</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0005795292090624571</v>
+        <v>0.001780896913260221</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0002788175770547241</v>
+        <v>0.001377356704324484</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.001504212617874146</v>
+        <v>0.001260086661204696</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0002601004380267113</v>
+        <v>0.005474394652992487</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.0001117676438298076</v>
+        <v>0.002373181981965899</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.001893191132694483</v>
+        <v>0.001121174427680671</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.006413866300135851</v>
+        <v>0.006753719877451658</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.001276677008718252</v>
+        <v>0.001711436430923641</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0007213803473860025</v>
+        <v>0.0007491346332244575</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.002690874738618731</v>
+        <v>0.00206560455262661</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.0007675081724300981</v>
+        <v>0.0003129383840132505</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.001758787431754172</v>
+        <v>0.0001590673346072435</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.001759008737280965</v>
+        <v>0.001011587446555495</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0005936048692092299</v>
+        <v>0.0005859289667569101</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.002278219908475876</v>
+        <v>0.001661435351707041</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0003647292323876172</v>
+        <v>0.001230277586728334</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0006365886656567454</v>
+        <v>0.0001910328574012965</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.004417384508997202</v>
+        <v>0.0005495583754964173</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.002049801871180534</v>
+        <v>0.0002871325705200434</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.00082809739978984</v>
+        <v>0.0008721887716092169</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.01176808774471283</v>
+        <v>0.0939936563372612</v>
       </c>
       <c r="B14" t="n">
-        <v>0.002014151774346828</v>
+        <v>0.03102952986955643</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02522194758057594</v>
+        <v>0.2669163644313812</v>
       </c>
       <c r="D14" t="n">
-        <v>0.04054945334792137</v>
+        <v>0.1105486750602722</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01381383650004864</v>
+        <v>0.004057325422763824</v>
       </c>
       <c r="F14" t="n">
-        <v>0.003444398753345013</v>
+        <v>0.0668853223323822</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001621434930711985</v>
+        <v>0.01707435585558414</v>
       </c>
       <c r="H14" t="n">
-        <v>0.002168769016861916</v>
+        <v>0.1083350330591202</v>
       </c>
       <c r="I14" t="n">
-        <v>0.003978594671934843</v>
+        <v>0.07151669263839722</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01215942576527596</v>
+        <v>0.049665167927742</v>
       </c>
       <c r="K14" t="n">
-        <v>0.003382564522325993</v>
+        <v>0.02098461613059044</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01618418656289577</v>
+        <v>0.2465559393167496</v>
       </c>
       <c r="M14" t="n">
-        <v>0.038132444024086</v>
+        <v>0.1068648621439934</v>
       </c>
       <c r="N14" t="n">
-        <v>0.001036005560308695</v>
+        <v>0.08247867226600647</v>
       </c>
       <c r="O14" t="n">
-        <v>0.006942013278603554</v>
+        <v>0.03983846306800842</v>
       </c>
       <c r="P14" t="n">
-        <v>0.003663003444671631</v>
+        <v>0.005377437919378281</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.004705044440925121</v>
+        <v>0.1277528554201126</v>
       </c>
       <c r="R14" t="n">
-        <v>0.002300792839378119</v>
+        <v>0.04552740231156349</v>
       </c>
       <c r="S14" t="n">
-        <v>0.008507917635142803</v>
+        <v>0.0004437929019331932</v>
       </c>
       <c r="T14" t="n">
-        <v>0.001717765931971371</v>
+        <v>0.03679977357387543</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0004309300857130438</v>
+        <v>0.03114373609423637</v>
       </c>
       <c r="V14" t="n">
-        <v>0.002845472190529108</v>
+        <v>0.07030364125967026</v>
       </c>
       <c r="W14" t="n">
-        <v>0.002870784606784582</v>
+        <v>0.03581459820270538</v>
       </c>
       <c r="X14" t="n">
-        <v>0.001013554283417761</v>
+        <v>0.05780232325196266</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.003992839250713587</v>
+        <v>0.02468187920749187</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.007060774136334658</v>
+        <v>0.002558016683906317</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.001071926904842257</v>
+        <v>0.02791579253971577</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0004151624743826687</v>
+        <v>0.006845391355454922</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.003014682326465845</v>
+        <v>0.01027773879468441</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.00200978247448802</v>
+        <v>0.04181097075343132</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.007315220311284065</v>
+        <v>0.08735424280166626</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.01130283437669277</v>
+        <v>0.09227174520492554</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.001222070888616145</v>
+        <v>0.01598288491368294</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0003610451240092516</v>
+        <v>0.006206339225172997</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.002022331580519676</v>
+        <v>0.0274111982434988</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.002012765966355801</v>
+        <v>0.04393021017313004</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.003696336643770337</v>
+        <v>0.007554907351732254</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.001455262769013643</v>
+        <v>0.009244766086339951</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.006971736438572407</v>
+        <v>0.03688689693808556</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.002242272719740868</v>
+        <v>0.05895503610372543</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.003051403444260359</v>
+        <v>0.04666146263480186</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.003566538216546178</v>
+        <v>0.07190647721290588</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.006675048731267452</v>
+        <v>0.03841507807374001</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.001036749687045813</v>
+        <v>0.02647802419960499</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.001225963467732072</v>
+        <v>0.008305596187710762</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.002781946212053299</v>
+        <v>0.02653906121850014</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.008129655383527279</v>
+        <v>0.00679545383900404</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.01191578898578882</v>
+        <v>0.186163142323494</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.02911788783967495</v>
+        <v>0.1402112543582916</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0005263326456770301</v>
+        <v>0.05189435184001923</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.009514773264527321</v>
+        <v>0.1113013923168182</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0007416345179080963</v>
+        <v>0.07658737897872925</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.01643155515193939</v>
+        <v>0.04865196347236633</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.004943400621414185</v>
+        <v>0.01493755355477333</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.01237508095800877</v>
+        <v>0.1097314059734344</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.007674762979149818</v>
+        <v>0.01540675200521946</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.002489909064024687</v>
+        <v>0.02306768670678139</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.006726774387061596</v>
+        <v>0.1389955878257751</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.02287806198000908</v>
+        <v>0.08446046710014343</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.003744204761460423</v>
+        <v>0.09122379869222641</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.009875531308352947</v>
+        <v>0.04344122111797333</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.01630851067602634</v>
+        <v>0.0535799041390419</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.005415922030806541</v>
+        <v>0.02452901937067509</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0001483587548136711</v>
+        <v>0.002615110948681831</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.006581505760550499</v>
+        <v>0.01467117667198181</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.004480082541704178</v>
+        <v>0.04298681765794754</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.00414245156571269</v>
+        <v>0.01345987431704998</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.009846074506640434</v>
+        <v>0.06135512143373489</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.004957376047968864</v>
+        <v>0.02412822842597961</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.0077651496976614</v>
+        <v>0.01150423381477594</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.001148240175098181</v>
+        <v>0.005522551015019417</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0009020644356496632</v>
+        <v>0.01017945446074009</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.002216067630797625</v>
+        <v>0.002876294776797295</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.004483893979340792</v>
+        <v>0.04756545275449753</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.00979905016720295</v>
+        <v>0.09484168887138367</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.01653385534882545</v>
+        <v>0.1971798539161682</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.003052077488973737</v>
+        <v>0.006722547113895416</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.005358564667403698</v>
+        <v>0.02800533547997475</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.003781870473176241</v>
+        <v>0.05155869200825691</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.01433523744344711</v>
+        <v>8.873455226421356e-05</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.003744262270629406</v>
+        <v>0.01390751451253891</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.002430294640362263</v>
+        <v>3.804219886660576e-05</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.0007163723930716515</v>
+        <v>0.0439176894724369</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.004921780899167061</v>
+        <v>0.06096230447292328</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.007205271627753973</v>
+        <v>0.02851514518260956</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.001853820635005832</v>
+        <v>0.004343835636973381</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.004248193930834532</v>
+        <v>0.009004502557218075</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.002255465602502227</v>
+        <v>0.00451361620798707</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.001083228271454573</v>
+        <v>0.007057122886180878</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.002655617659911513</v>
+        <v>0.01492085494101048</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.007446655072271824</v>
+        <v>0.007705236785113811</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0005569227505475283</v>
+        <v>0.07202645391225815</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.003364396980032325</v>
+        <v>0.004582126624882221</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.004043522290885448</v>
+        <v>0.01235029473900795</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.000905050546862185</v>
+        <v>0.1147745102643967</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.001198494806885719</v>
+        <v>0.01325846277177334</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.004360965918749571</v>
+        <v>0.01442076079547405</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.01066805236041546</v>
+        <v>0.00231070863083005</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.002614915370941162</v>
+        <v>0.04267755895853043</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.002199519891291857</v>
+        <v>0.01151795592159033</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.001333816209807992</v>
+        <v>0.02029455825686455</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.003797694342210889</v>
+        <v>0.05690667778253555</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.005360471084713936</v>
+        <v>0.03004195168614388</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.003598525887355208</v>
+        <v>0.004155697301030159</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.003108717035502195</v>
+        <v>0.01797965168952942</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.001454026205465198</v>
+        <v>0.01433508656919003</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0003809767076745629</v>
+        <v>0.0004676543176174164</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.003323788987472653</v>
+        <v>0.02245838567614555</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.00297128246165812</v>
+        <v>0.01147384569048882</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.01036555133759975</v>
+        <v>0.004627363756299019</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.005220081657171249</v>
+        <v>0.1247738152742386</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.009988108649849892</v>
+        <v>0.03394579142332077</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.008731898851692677</v>
+        <v>0.07555722445249557</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.01462820637971163</v>
+        <v>0.02894693799316883</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.01770354248583317</v>
+        <v>0.06855458766222</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.005839377176016569</v>
+        <v>0.03349845856428146</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.003467389149591327</v>
+        <v>0.08753811568021774</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0001806914806365967</v>
+        <v>0.01812662556767464</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.003164332592859864</v>
+        <v>0.006882318295538425</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.006002132780849934</v>
+        <v>0.01268549729138613</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0008330901619046926</v>
+        <v>0.01728129386901855</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.001910775667056441</v>
+        <v>0.03258505091071129</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0008831610321067274</v>
+        <v>0.03294433280825615</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.002066996414214373</v>
+        <v>0.04742259532213211</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.007670820225030184</v>
+        <v>0.01538953930139542</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.008455239236354828</v>
+        <v>0.03812434524297714</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.003237559925764799</v>
+        <v>0.05806600302457809</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.002319543855264783</v>
+        <v>0.006620088592171669</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.001936289947479963</v>
+        <v>0.01629631780087948</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.006514834240078926</v>
+        <v>0.01517579145729542</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.006628824397921562</v>
+        <v>0.04840457439422607</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.006125517655164003</v>
+        <v>0.04243405908346176</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.00517400074750185</v>
+        <v>0.03596962243318558</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.01075929496437311</v>
+        <v>0.009479399770498276</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0005331338616088033</v>
+        <v>0.007108123973011971</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.003091188846156001</v>
+        <v>0.0280721765011549</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0007112342864274979</v>
+        <v>0.03294878080487251</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.004838221706449986</v>
+        <v>0.04836586117744446</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.01079384796321392</v>
+        <v>0.004009387455880642</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.002192302839830518</v>
+        <v>0.02208616957068443</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.003257546108216047</v>
+        <v>0.002262829802930355</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.001424434827640653</v>
+        <v>0.009326159954071045</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.001205285778269172</v>
+        <v>0.01796065829694271</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.003010132582858205</v>
+        <v>0.003009724896401167</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.003964869305491447</v>
+        <v>0.02413873746991158</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.001617606962099671</v>
+        <v>0.05584484711289406</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.005544622428715229</v>
+        <v>0.01916645467281342</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.001048065489158034</v>
+        <v>0.03242378681898117</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.007509713061153889</v>
+        <v>0.03530749306082726</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.0023743468336761</v>
+        <v>0.08174488693475723</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.00152025290299207</v>
+        <v>0.003250539302825928</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.01671217381954193</v>
+        <v>0.03987730294466019</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.005400828085839748</v>
+        <v>0.003492349060252309</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.001807112246751785</v>
+        <v>0.0005481033585965633</v>
       </c>
       <c r="EY14" t="n">
-        <v>2.737692557275295e-05</v>
+        <v>0.04662266001105309</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.004341104067862034</v>
+        <v>0.05960483476519585</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.006000611465424299</v>
+        <v>0.03485380485653877</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.002080692909657955</v>
+        <v>0.00616172794252634</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.003535854863002896</v>
+        <v>0.0266038253903389</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0001824395731091499</v>
+        <v>0.01062976010143757</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.0006516510620713234</v>
+        <v>0.008664924651384354</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.005342088174074888</v>
+        <v>0.01728077605366707</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0004198650713078678</v>
+        <v>0.02580273896455765</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.002233585342764854</v>
+        <v>0.02020885050296783</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.001793552772141993</v>
+        <v>0.1002649292349815</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.006336201447993517</v>
+        <v>0.05515468120574951</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.006373666226863861</v>
+        <v>0.06091112270951271</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0004596408107317984</v>
+        <v>0.06580821424722672</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.00402407068759203</v>
+        <v>0.01055526360869408</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.004191787913441658</v>
+        <v>0.01620590686798096</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.009389268234372139</v>
+        <v>0.004778070375323296</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.008703842759132385</v>
+        <v>0.0147450715303421</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.004234928637742996</v>
+        <v>0.01506222225725651</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.01051238738000393</v>
+        <v>0.04023998975753784</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.00697239488363266</v>
+        <v>0.06146064773201942</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.003835329320281744</v>
+        <v>0.01586315222084522</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.001846209052018821</v>
+        <v>0.05950631946325302</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0007032378343865275</v>
+        <v>0.03994626924395561</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.001527767861261964</v>
+        <v>0.08087550848722458</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.005619592498987913</v>
+        <v>0.06732689589262009</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.003709554905071855</v>
+        <v>0.0009616240859031677</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.003768677124753594</v>
+        <v>0.1050617173314095</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.00469429325312376</v>
+        <v>0.05767324939370155</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.000750792445614934</v>
+        <v>0.03745733201503754</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.006679599173367023</v>
+        <v>0.008938232436776161</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.005012476816773415</v>
+        <v>0.01150919497013092</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.004668280016630888</v>
+        <v>0.005720921792089939</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.01351066678762436</v>
+        <v>0.03488605469465256</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.01154906395822763</v>
+        <v>0.0203840471804142</v>
       </c>
     </row>
     <row r="15">
@@ -8965,571 +8965,571 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4.170342072029598e-05</v>
+        <v>0.1931090354919434</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0005887980805709958</v>
+        <v>0.07571513205766678</v>
       </c>
       <c r="C16" t="n">
-        <v>6.865425530122593e-05</v>
+        <v>0.1490893959999084</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0001445385860279202</v>
+        <v>0.1257978230714798</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0002356826444156468</v>
+        <v>0.07467277348041534</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0006572100101038814</v>
+        <v>0.2315695434808731</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001103320464608259</v>
+        <v>0.05026765912771225</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0003182940999977291</v>
+        <v>0.1696553826332092</v>
       </c>
       <c r="I16" t="n">
-        <v>1.680189598118886e-05</v>
+        <v>0.06295682489871979</v>
       </c>
       <c r="J16" t="n">
-        <v>4.427934618433937e-05</v>
+        <v>0.1362570524215698</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0004969845758751035</v>
+        <v>0.1137716844677925</v>
       </c>
       <c r="L16" t="n">
-        <v>8.532005449524149e-05</v>
+        <v>0.1927020698785782</v>
       </c>
       <c r="M16" t="n">
-        <v>8.372231968678534e-05</v>
+        <v>0.1160767748951912</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0001309081126237288</v>
+        <v>0.1173106133937836</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0005974463419988751</v>
+        <v>0.2367330938577652</v>
       </c>
       <c r="P16" t="n">
-        <v>9.392481297254562e-05</v>
+        <v>0.08452827483415604</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0002268076641485095</v>
+        <v>0.1730778366327286</v>
       </c>
       <c r="R16" t="n">
-        <v>1.980045635718852e-05</v>
+        <v>0.0892389714717865</v>
       </c>
       <c r="S16" t="n">
-        <v>2.881731234083418e-06</v>
+        <v>0.03875044733285904</v>
       </c>
       <c r="T16" t="n">
-        <v>6.234632746782154e-05</v>
+        <v>0.05652099102735519</v>
       </c>
       <c r="U16" t="n">
-        <v>2.151814805984031e-05</v>
+        <v>0.02320142462849617</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0001370373647660017</v>
+        <v>0.02285515889525414</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0001745331974234432</v>
+        <v>0.03151430189609528</v>
       </c>
       <c r="X16" t="n">
-        <v>1.912016341520939e-05</v>
+        <v>0.02596515789628029</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.858005796559155e-06</v>
+        <v>0.01445645093917847</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.059143586549908e-05</v>
+        <v>0.04495948553085327</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.65572164405603e-05</v>
+        <v>0.00291715725325048</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.99526984943077e-05</v>
+        <v>0.07850604504346848</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.821111724595539e-05</v>
+        <v>0.08712540566921234</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.488405723648611e-05</v>
+        <v>0.007058971561491489</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.350709792153793e-06</v>
+        <v>0.1342915147542953</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.509360976750031e-05</v>
+        <v>0.07455578446388245</v>
       </c>
       <c r="AG16" t="n">
-        <v>5.085988595965318e-05</v>
+        <v>0.08336605876684189</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.131828659912571e-05</v>
+        <v>0.0204525925219059</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.283192225149833e-05</v>
+        <v>0.08606268465518951</v>
       </c>
       <c r="AJ16" t="n">
-        <v>7.997872671694495e-06</v>
+        <v>0.0478770025074482</v>
       </c>
       <c r="AK16" t="n">
-        <v>7.199474202934653e-05</v>
+        <v>0.06521470099687576</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0001026944155455567</v>
+        <v>0.09776829928159714</v>
       </c>
       <c r="AM16" t="n">
-        <v>4.456278111319989e-05</v>
+        <v>0.000393059104681015</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.212645474879537e-05</v>
+        <v>0.01714164204895496</v>
       </c>
       <c r="AO16" t="n">
-        <v>2.013742414419539e-05</v>
+        <v>0.09275756031274796</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0001025681995088235</v>
+        <v>0.0597376637160778</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.079381374642253e-05</v>
+        <v>0.03877862170338631</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.467041410156526e-05</v>
+        <v>0.02985656261444092</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.864827547455207e-05</v>
+        <v>0.003027412109076977</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.648670073947869e-05</v>
+        <v>0.03654897212982178</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.0003699818335007876</v>
+        <v>0.3110013008117676</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.359451021533459e-05</v>
+        <v>0.01859697140753269</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.0001105414630728774</v>
+        <v>0.04252305254340172</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.0001529970613773912</v>
+        <v>0.01787462085485458</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.0003590255219023675</v>
+        <v>0.1500262767076492</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9.506788774160668e-05</v>
+        <v>0.07711350917816162</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.270748417591676e-05</v>
+        <v>0.09176266193389893</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.867615643888712e-06</v>
+        <v>0.02872938849031925</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.113037382718176e-05</v>
+        <v>0.1148545145988464</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.0002075832744594663</v>
+        <v>0.1128540709614754</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0001201567138195969</v>
+        <v>0.05516238510608673</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.003306897473522e-05</v>
+        <v>0.02980530075728893</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.0001609659957466647</v>
+        <v>0.1038113012909889</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.0002049799222731963</v>
+        <v>0.006839616224169731</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.197382673330139e-05</v>
+        <v>0.0289900116622448</v>
       </c>
       <c r="BJ16" t="n">
-        <v>6.150550325401127e-05</v>
+        <v>0.03554929047822952</v>
       </c>
       <c r="BK16" t="n">
-        <v>2.246151780127548e-05</v>
+        <v>0.003974208608269691</v>
       </c>
       <c r="BL16" t="n">
-        <v>7.459877815563232e-05</v>
+        <v>0.01497065462172031</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0001761233434081078</v>
+        <v>0.03013074956834316</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.61108099645935e-05</v>
+        <v>0.1143705397844315</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.268737105419859e-05</v>
+        <v>0.00946691632270813</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.415298851905391e-05</v>
+        <v>0.06550144404172897</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.282320514903404e-05</v>
+        <v>0.008085928857326508</v>
       </c>
       <c r="BR16" t="n">
-        <v>3.735894279088825e-05</v>
+        <v>0.08891412615776062</v>
       </c>
       <c r="BS16" t="n">
-        <v>6.491109161288477e-06</v>
+        <v>0.008728290908038616</v>
       </c>
       <c r="BT16" t="n">
-        <v>2.82851469819434e-05</v>
+        <v>0.05623498558998108</v>
       </c>
       <c r="BU16" t="n">
-        <v>2.41530651692301e-05</v>
+        <v>0.03681160882115364</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.0002235281281173229</v>
+        <v>0.1452384144067764</v>
       </c>
       <c r="BW16" t="n">
-        <v>3.440312866587192e-06</v>
+        <v>0.03073801845312119</v>
       </c>
       <c r="BX16" t="n">
-        <v>6.472258974099532e-05</v>
+        <v>0.06939563900232315</v>
       </c>
       <c r="BY16" t="n">
-        <v>6.933362328709336e-06</v>
+        <v>0.02227259799838066</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0001568708830745891</v>
+        <v>0.1229231283068657</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.388185501127737e-05</v>
+        <v>0.04575029388070107</v>
       </c>
       <c r="CB16" t="n">
-        <v>2.900975596276112e-05</v>
+        <v>0.03796815499663353</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.527028846088797e-05</v>
+        <v>0.01417354308068752</v>
       </c>
       <c r="CD16" t="n">
-        <v>9.502291504759341e-06</v>
+        <v>0.01227767672389746</v>
       </c>
       <c r="CE16" t="n">
-        <v>6.753498018952087e-05</v>
+        <v>0.03872224316000938</v>
       </c>
       <c r="CF16" t="n">
-        <v>1.836782939790282e-05</v>
+        <v>0.05309130251407623</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.350239421706647e-05</v>
+        <v>0.02414187043905258</v>
       </c>
       <c r="CH16" t="n">
-        <v>4.327176429796964e-05</v>
+        <v>0.004218412563204765</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.0001235537347383797</v>
+        <v>0.05611397698521614</v>
       </c>
       <c r="CJ16" t="n">
-        <v>4.574592821882106e-05</v>
+        <v>0.03366269916296005</v>
       </c>
       <c r="CK16" t="n">
-        <v>5.395443440647796e-05</v>
+        <v>0.00498195318505168</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.925222361227497e-06</v>
+        <v>0.01612254045903683</v>
       </c>
       <c r="CM16" t="n">
-        <v>6.138467870187014e-05</v>
+        <v>0.02838216349482536</v>
       </c>
       <c r="CN16" t="n">
-        <v>5.126625183038414e-05</v>
+        <v>0.1227537915110588</v>
       </c>
       <c r="CO16" t="n">
-        <v>4.408723543747328e-05</v>
+        <v>0.02589575946331024</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.619941394892521e-05</v>
+        <v>0.02362184599041939</v>
       </c>
       <c r="CQ16" t="n">
-        <v>6.066275818739086e-05</v>
+        <v>0.02803192473948002</v>
       </c>
       <c r="CR16" t="n">
-        <v>3.865648977807723e-05</v>
+        <v>0.03157727047801018</v>
       </c>
       <c r="CS16" t="n">
-        <v>7.775463745929301e-05</v>
+        <v>0.003782885149121284</v>
       </c>
       <c r="CT16" t="n">
-        <v>7.446870586136356e-05</v>
+        <v>0.02420142665505409</v>
       </c>
       <c r="CU16" t="n">
-        <v>8.821615665510762e-06</v>
+        <v>0.009509996511042118</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.526060143281939e-06</v>
+        <v>3.665871918201447e-05</v>
       </c>
       <c r="CW16" t="n">
-        <v>5.137766129337251e-05</v>
+        <v>0.01873902603983879</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.138368679676205e-05</v>
+        <v>0.03870467469096184</v>
       </c>
       <c r="CY16" t="n">
-        <v>5.026788130635396e-05</v>
+        <v>0.01947038620710373</v>
       </c>
       <c r="CZ16" t="n">
-        <v>3.489264781819656e-05</v>
+        <v>0.0130714550614357</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.0001175447614514269</v>
+        <v>0.05816441401839256</v>
       </c>
       <c r="DB16" t="n">
-        <v>3.283790283603594e-05</v>
+        <v>0.01114597544074059</v>
       </c>
       <c r="DC16" t="n">
-        <v>6.341443804558367e-05</v>
+        <v>0.02044135145843029</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.865713602455799e-05</v>
+        <v>0.0178286787122488</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.0001064880125341006</v>
+        <v>0.07117543369531631</v>
       </c>
       <c r="DF16" t="n">
-        <v>4.354416523710825e-05</v>
+        <v>0.03480004891753197</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.910463783540763e-05</v>
+        <v>0.01595053821802139</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0003149841795675457</v>
+        <v>0.03210918232798576</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.0001270894426852465</v>
+        <v>0.01414390653371811</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.940615922852885e-05</v>
+        <v>0.06704546511173248</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.15433241869323e-05</v>
+        <v>0.04915991798043251</v>
       </c>
       <c r="DL16" t="n">
-        <v>2.798877540044487e-05</v>
+        <v>0.03860679268836975</v>
       </c>
       <c r="DM16" t="n">
-        <v>9.157329623121768e-05</v>
+        <v>0.04180724918842316</v>
       </c>
       <c r="DN16" t="n">
-        <v>3.220912913093343e-05</v>
+        <v>0.008659560233354568</v>
       </c>
       <c r="DO16" t="n">
-        <v>3.024922261829488e-05</v>
+        <v>0.03416884690523148</v>
       </c>
       <c r="DP16" t="n">
-        <v>2.477450289006811e-05</v>
+        <v>0.009333739057183266</v>
       </c>
       <c r="DQ16" t="n">
-        <v>2.233031955256592e-05</v>
+        <v>0.007533770520240068</v>
       </c>
       <c r="DR16" t="n">
-        <v>2.009871241170913e-05</v>
+        <v>0.06513319909572601</v>
       </c>
       <c r="DS16" t="n">
-        <v>7.270227797562256e-05</v>
+        <v>0.02635977789759636</v>
       </c>
       <c r="DT16" t="n">
-        <v>6.276004569372162e-05</v>
+        <v>0.02097088471055031</v>
       </c>
       <c r="DU16" t="n">
-        <v>1.390214492857922e-05</v>
+        <v>0.03531918302178383</v>
       </c>
       <c r="DV16" t="n">
-        <v>2.515968662919477e-05</v>
+        <v>0.07159585505723953</v>
       </c>
       <c r="DW16" t="n">
-        <v>8.312279533129185e-06</v>
+        <v>0.0045913215726614</v>
       </c>
       <c r="DX16" t="n">
-        <v>4.423937207320705e-05</v>
+        <v>0.08073683083057404</v>
       </c>
       <c r="DY16" t="n">
-        <v>1.068054734787438e-05</v>
+        <v>0.02176625281572342</v>
       </c>
       <c r="DZ16" t="n">
-        <v>6.730225868523121e-05</v>
+        <v>0.006443317979574203</v>
       </c>
       <c r="EA16" t="n">
-        <v>1.466297908336855e-05</v>
+        <v>0.04468993842601776</v>
       </c>
       <c r="EB16" t="n">
-        <v>4.723273013951257e-05</v>
+        <v>0.009444931522011757</v>
       </c>
       <c r="EC16" t="n">
-        <v>4.623288987204432e-07</v>
+        <v>0.007929867133498192</v>
       </c>
       <c r="ED16" t="n">
-        <v>2.872765799111221e-05</v>
+        <v>0.06756002455949783</v>
       </c>
       <c r="EE16" t="n">
-        <v>4.355934652267024e-05</v>
+        <v>0.02328367345035076</v>
       </c>
       <c r="EF16" t="n">
-        <v>4.32783599535469e-06</v>
+        <v>0.06951002776622772</v>
       </c>
       <c r="EG16" t="n">
-        <v>3.896896669175476e-05</v>
+        <v>0.006973163224756718</v>
       </c>
       <c r="EH16" t="n">
-        <v>1.596530455572065e-05</v>
+        <v>0.0427209697663784</v>
       </c>
       <c r="EI16" t="n">
-        <v>1.724843968986534e-05</v>
+        <v>0.04980693757534027</v>
       </c>
       <c r="EJ16" t="n">
-        <v>3.52352908521425e-05</v>
+        <v>0.02565992623567581</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.0001062690062099136</v>
+        <v>0.011713657528162</v>
       </c>
       <c r="EL16" t="n">
-        <v>3.90485038224142e-05</v>
+        <v>0.01657875441014767</v>
       </c>
       <c r="EM16" t="n">
-        <v>1.263000376638956e-05</v>
+        <v>0.007264303974807262</v>
       </c>
       <c r="EN16" t="n">
-        <v>8.20883724372834e-06</v>
+        <v>0.01946721039712429</v>
       </c>
       <c r="EO16" t="n">
-        <v>2.744818993960507e-05</v>
+        <v>0.03374979645013809</v>
       </c>
       <c r="EP16" t="n">
-        <v>6.291320460150018e-07</v>
+        <v>0.002969861030578613</v>
       </c>
       <c r="EQ16" t="n">
-        <v>5.875044735148549e-06</v>
+        <v>0.01558912079781294</v>
       </c>
       <c r="ER16" t="n">
-        <v>1.416828490619082e-05</v>
+        <v>0.07423466444015503</v>
       </c>
       <c r="ES16" t="n">
-        <v>7.529793219873682e-05</v>
+        <v>0.03608174622058868</v>
       </c>
       <c r="ET16" t="n">
-        <v>5.049299579695798e-05</v>
+        <v>0.09586438536643982</v>
       </c>
       <c r="EU16" t="n">
-        <v>2.217235305579379e-06</v>
+        <v>0.01984399929642677</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.0001903712109196931</v>
+        <v>0.05506442114710808</v>
       </c>
       <c r="EW16" t="n">
-        <v>7.02882680343464e-05</v>
+        <v>0.05341973155736923</v>
       </c>
       <c r="EX16" t="n">
-        <v>4.11146220358205e-06</v>
+        <v>0.004936285316944122</v>
       </c>
       <c r="EY16" t="n">
-        <v>4.417751915752888e-05</v>
+        <v>0.04784687608480453</v>
       </c>
       <c r="EZ16" t="n">
-        <v>9.566956578055397e-07</v>
+        <v>0.04212802648544312</v>
       </c>
       <c r="FA16" t="n">
-        <v>3.270948582212441e-05</v>
+        <v>0.01534136105328798</v>
       </c>
       <c r="FB16" t="n">
-        <v>4.85528762510512e-05</v>
+        <v>7.678777910768986e-05</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.0001217626486322843</v>
+        <v>0.06423813104629517</v>
       </c>
       <c r="FD16" t="n">
-        <v>5.369599239202216e-05</v>
+        <v>0.02643204294145107</v>
       </c>
       <c r="FE16" t="n">
-        <v>4.984609404345974e-05</v>
+        <v>0.005296362098306417</v>
       </c>
       <c r="FF16" t="n">
-        <v>4.559396074910183e-06</v>
+        <v>0.009504577144980431</v>
       </c>
       <c r="FG16" t="n">
-        <v>3.311438922537491e-05</v>
+        <v>0.03395767882466316</v>
       </c>
       <c r="FH16" t="n">
-        <v>9.462684101890773e-05</v>
+        <v>0.03278788179159164</v>
       </c>
       <c r="FI16" t="n">
-        <v>3.416855906834826e-05</v>
+        <v>0.005799712613224983</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.00012315230560489</v>
+        <v>0.04224064201116562</v>
       </c>
       <c r="FK16" t="n">
-        <v>5.565161700360477e-06</v>
+        <v>0.01336431317031384</v>
       </c>
       <c r="FL16" t="n">
-        <v>6.0946407757001e-05</v>
+        <v>0.1049267947673798</v>
       </c>
       <c r="FM16" t="n">
-        <v>7.609755357407266e-06</v>
+        <v>0.02695087529718876</v>
       </c>
       <c r="FN16" t="n">
-        <v>7.09013911546208e-05</v>
+        <v>0.04591332376003265</v>
       </c>
       <c r="FO16" t="n">
-        <v>2.561193832661957e-05</v>
+        <v>0.05833512917160988</v>
       </c>
       <c r="FP16" t="n">
-        <v>6.431774818338454e-05</v>
+        <v>0.03692967444658279</v>
       </c>
       <c r="FQ16" t="n">
-        <v>2.550565841374919e-05</v>
+        <v>0.02138349786400795</v>
       </c>
       <c r="FR16" t="n">
-        <v>3.678487337310798e-05</v>
+        <v>0.03617014735937119</v>
       </c>
       <c r="FS16" t="n">
-        <v>4.612578050000593e-05</v>
+        <v>0.08952821046113968</v>
       </c>
       <c r="FT16" t="n">
-        <v>9.843506632023491e-08</v>
+        <v>0.2347418367862701</v>
       </c>
       <c r="FU16" t="n">
-        <v>8.267520024674013e-05</v>
+        <v>0.02702886983752251</v>
       </c>
       <c r="FV16" t="n">
-        <v>8.967269968707114e-05</v>
+        <v>0.01849798671901226</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.0001052736915880814</v>
+        <v>0.03244620189070702</v>
       </c>
       <c r="FX16" t="n">
-        <v>2.047043199127074e-05</v>
+        <v>0.1298175901174545</v>
       </c>
       <c r="FY16" t="n">
-        <v>5.835359843331389e-05</v>
+        <v>0.001551822759211063</v>
       </c>
       <c r="FZ16" t="n">
-        <v>5.216883073444478e-05</v>
+        <v>0.02255096845328808</v>
       </c>
       <c r="GA16" t="n">
-        <v>3.750473479158245e-05</v>
+        <v>0.04911362379789352</v>
       </c>
       <c r="GB16" t="n">
-        <v>3.237197233829647e-06</v>
+        <v>0.1004934906959534</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.0001931325678015128</v>
+        <v>0.0296694952994585</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.0001150694952229969</v>
+        <v>0.002900660503655672</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.0001193393036373891</v>
+        <v>0.01047601364552975</v>
       </c>
       <c r="GF16" t="n">
-        <v>8.760226592130493e-06</v>
+        <v>0.0160808376967907</v>
       </c>
       <c r="GG16" t="n">
-        <v>1.496172262704931e-05</v>
+        <v>0.02399458549916744</v>
       </c>
     </row>
   </sheetData>
